--- a/Portfolio.xlsx
+++ b/Portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\john.hcpang\Documents\Practice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD848B31-1DDF-4E2E-A21D-9020DA1BD2DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF1D40DF-39C4-4A99-BFCE-B6D0135782D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{E7CDDCE8-D664-4969-9A02-FA9A05E60C5E}"/>
   </bookViews>
@@ -845,8 +845,8 @@
         <v>4701.25361118</v>
       </c>
       <c r="E2" s="17">
-        <f t="shared" ref="E2:E18" si="0">D2/($D$20+$D$22+$D$23+$B$27+$B$26)</f>
-        <v>9.1478992287180302E-2</v>
+        <f>D2/($D$19+$D$22+$D$23+$B$27+$B$26)</f>
+        <v>9.1256904271929298E-2</v>
       </c>
       <c r="G2" s="46" t="s">
         <v>42</v>
@@ -874,8 +874,8 @@
         <v>17345.2587561</v>
       </c>
       <c r="E3" s="17">
-        <f t="shared" si="0"/>
-        <v>0.33751142210133928</v>
+        <f>D3/($D$19+$D$22+$D$23+$B$27+$B$26)</f>
+        <v>0.33669202914581003</v>
       </c>
       <c r="G3" s="46" t="s">
         <v>45</v>
@@ -903,8 +903,8 @@
         <v>1336.4440999999999</v>
       </c>
       <c r="E4" s="17">
-        <f t="shared" si="0"/>
-        <v>2.6005097709557855E-2</v>
+        <f>D4/($D$19+$D$22+$D$23+$B$27+$B$26)</f>
+        <v>2.5941963864373013E-2</v>
       </c>
       <c r="G4" s="33"/>
       <c r="H4" s="33"/>
@@ -927,8 +927,8 @@
         <v>1981.6799999999998</v>
       </c>
       <c r="E5" s="17">
-        <f t="shared" si="0"/>
-        <v>3.8560372281247389E-2</v>
+        <f>D5/($D$19+$D$22+$D$23+$B$27+$B$26)</f>
+        <v>3.8466757383081501E-2</v>
       </c>
       <c r="G5" s="33"/>
       <c r="H5" s="33"/>
@@ -947,12 +947,12 @@
         <v>301.79500000000002</v>
       </c>
       <c r="D6" s="15">
-        <f t="shared" ref="D6:D7" si="1">C6*B6</f>
+        <f t="shared" ref="D6:D7" si="0">C6*B6</f>
         <v>1810.77</v>
       </c>
       <c r="E6" s="17">
-        <f t="shared" si="0"/>
-        <v>3.5234732810400439E-2</v>
+        <f>D6/($D$19+$D$22+$D$23+$B$27+$B$26)</f>
+        <v>3.5149191729523688E-2</v>
       </c>
       <c r="G6" s="33"/>
       <c r="H6" s="33"/>
@@ -971,12 +971,12 @@
         <v>71.781999999999996</v>
       </c>
       <c r="D7" s="39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1076.73</v>
       </c>
       <c r="E7" s="17">
-        <f t="shared" si="0"/>
-        <v>2.095147029105986E-2</v>
+        <f>D7/($D$19+$D$22+$D$23+$B$27+$B$26)</f>
+        <v>2.0900605383858822E-2</v>
       </c>
       <c r="G7" s="33"/>
       <c r="H7" s="33"/>
@@ -999,8 +999,8 @@
         <v>2883.78</v>
       </c>
       <c r="E8" s="17">
-        <f t="shared" si="0"/>
-        <v>5.6113817759282834E-2</v>
+        <f>D8/($D$19+$D$22+$D$23+$B$27+$B$26)</f>
+        <v>5.5977587504633837E-2</v>
       </c>
       <c r="G8" s="33"/>
       <c r="H8" s="33"/>
@@ -1023,8 +1023,8 @@
         <v>6820.1280000000006</v>
       </c>
       <c r="E9" s="17">
-        <f t="shared" si="0"/>
-        <v>0.13270895133712771</v>
+        <f>D9/($D$19+$D$22+$D$23+$B$27+$B$26)</f>
+        <v>0.1323867673375928</v>
       </c>
       <c r="M9" s="37"/>
     </row>
@@ -1039,12 +1039,12 @@
         <v>93.789000000000001</v>
       </c>
       <c r="D10" s="19">
-        <f t="shared" ref="D10:D18" si="2">C10*B10</f>
+        <f t="shared" ref="D10:D18" si="1">C10*B10</f>
         <v>844.101</v>
       </c>
       <c r="E10" s="17">
-        <f t="shared" si="0"/>
-        <v>1.642487626810242E-2</v>
+        <f>D10/($D$19+$D$22+$D$23+$B$27+$B$26)</f>
+        <v>1.6385000794182956E-2</v>
       </c>
       <c r="G10" s="33"/>
       <c r="H10" s="33"/>
@@ -1063,12 +1063,12 @@
         <v>181.05799999999999</v>
       </c>
       <c r="D11" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>651.80880000000002</v>
       </c>
       <c r="E11" s="17">
-        <f t="shared" si="0"/>
-        <v>1.2683172855452507E-2</v>
+        <f>D11/($D$19+$D$22+$D$23+$B$27+$B$26)</f>
+        <v>1.2652381297564439E-2</v>
       </c>
       <c r="F11"/>
       <c r="G11" s="33"/>
@@ -1198,12 +1198,12 @@
         <v>62.938000000000002</v>
       </c>
       <c r="D12" s="40">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>629.38</v>
       </c>
       <c r="E12" s="17">
-        <f t="shared" si="0"/>
-        <v>1.2246743725713275E-2</v>
+        <f>D12/($D$19+$D$22+$D$23+$B$27+$B$26)</f>
+        <v>1.2217011708128375E-2</v>
       </c>
       <c r="J12" s="33"/>
       <c r="K12" s="33"/>
@@ -1220,11 +1220,11 @@
         <v>0</v>
       </c>
       <c r="D13" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E13" s="17">
-        <f t="shared" si="0"/>
+        <f>D13/($D$19+$D$22+$D$23+$B$27+$B$26)</f>
         <v>0</v>
       </c>
       <c r="J13" s="33"/>
@@ -1242,12 +1242,12 @@
         <v>210.02</v>
       </c>
       <c r="D14" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>210.02</v>
       </c>
       <c r="E14" s="17">
-        <f t="shared" si="0"/>
-        <v>4.0866584849761703E-3</v>
+        <f>D14/($D$19+$D$22+$D$23+$B$27+$B$26)</f>
+        <v>4.076737104676223E-3</v>
       </c>
       <c r="J14" s="33"/>
       <c r="K14" s="33"/>
@@ -1268,8 +1268,8 @@
         <v>3450.5879999999997</v>
       </c>
       <c r="E15" s="17">
-        <f t="shared" si="0"/>
-        <v>6.7143008896090622E-2</v>
+        <f>D15/($D$19+$D$22+$D$23+$B$27+$B$26)</f>
+        <v>6.6980002535713346E-2</v>
       </c>
       <c r="G15" s="33"/>
       <c r="H15" s="33"/>
@@ -1293,8 +1293,8 @@
         <v>644.79999999999995</v>
       </c>
       <c r="E16" s="17">
-        <f t="shared" si="0"/>
-        <v>1.2546792644094059E-2</v>
+        <f>D16/($D$19+$D$22+$D$23+$B$27+$B$26)</f>
+        <v>1.2516332183102696E-2</v>
       </c>
       <c r="J16" s="33"/>
       <c r="K16" s="33"/>
@@ -1311,12 +1311,12 @@
         <v>100.62</v>
       </c>
       <c r="D17" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>2314.2600000000002</v>
       </c>
       <c r="E17" s="17">
-        <f t="shared" si="0"/>
-        <v>4.5031855373016627E-2</v>
+        <f>D17/($D$19+$D$22+$D$23+$B$27+$B$26)</f>
+        <v>4.4922529339434324E-2</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
@@ -1330,12 +1330,18 @@
         <v>29.497</v>
       </c>
       <c r="D18" s="19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>855.41300000000001</v>
       </c>
       <c r="E18" s="50">
-        <f t="shared" si="0"/>
-        <v>1.664498997528293E-2</v>
+        <f>D18/($D$19+$D$22+$D$23+$B$27+$B$26)</f>
+        <v>1.6604580120571383E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="D19" s="20">
+        <f>SUM(D2:D18)</f>
+        <v>47556.415267280005</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
@@ -1344,10 +1350,6 @@
       </c>
       <c r="B20" s="42"/>
       <c r="C20" s="42"/>
-      <c r="D20" s="20">
-        <f>SUM(D2:D18)</f>
-        <v>47556.415267280005</v>
-      </c>
       <c r="E20" s="34"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
@@ -1385,8 +1387,8 @@
         <v>977.64119292939995</v>
       </c>
       <c r="E22" s="16">
-        <f>D22/(D20+D22+D23+B26+B72)</f>
-        <v>1.9062137739616476E-2</v>
+        <f>D22/(D19+D22+D23+B26+B72)</f>
+        <v>1.9015765547727381E-2</v>
       </c>
       <c r="H22" s="48"/>
       <c r="J22" s="33"/>
@@ -1398,18 +1400,18 @@
         <v>25</v>
       </c>
       <c r="B23" s="11">
-        <v>3.3500000000000001E-3</v>
+        <v>5.4400000000000004E-3</v>
       </c>
       <c r="C23" s="15">
-        <v>74929.42</v>
+        <v>69132.929999999993</v>
       </c>
       <c r="D23" s="24">
         <f>C23*B23</f>
-        <v>251.01355699999999</v>
+        <v>376.08313920000001</v>
       </c>
       <c r="E23" s="16">
-        <f>D23/(D20+D22+D23+B26+B27)</f>
-        <v>4.8843285523193008E-3</v>
+        <f>D23/(D19+D22+D23+B26+B27)</f>
+        <v>7.3002194458611225E-3</v>
       </c>
       <c r="J23" s="33"/>
       <c r="K23" s="33"/>
@@ -1441,7 +1443,7 @@
         <v>2502</v>
       </c>
       <c r="C26" s="43">
-        <f>B26/(D20+B27)</f>
+        <f>B26/(D19+B27)</f>
         <v>5.2495789499203908E-2</v>
       </c>
       <c r="D26" s="26"/>
@@ -1458,7 +1460,7 @@
         <v>104.55</v>
       </c>
       <c r="C27" s="43">
-        <f>B27/D20</f>
+        <f>B27/D19</f>
         <v>2.1984415648740666E-3</v>
       </c>
       <c r="D27" s="26"/>
@@ -1570,7 +1572,7 @@
       <c r="G32" s="15"/>
       <c r="I32" s="15">
         <f>66511.1*B23+66511.1*B22</f>
-        <v>1073.0508458510001</v>
+        <v>1212.0590448510002</v>
       </c>
       <c r="J32" s="33"/>
       <c r="K32" s="33"/>
@@ -1609,7 +1611,7 @@
       <c r="G34" s="15"/>
       <c r="I34" s="35">
         <f>SUM(I30:I32)</f>
-        <v>52352.670845850997</v>
+        <v>52491.679044850993</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -1634,8 +1636,8 @@
       <c r="G35" s="15"/>
       <c r="H35" s="9"/>
       <c r="I35" s="15">
-        <f>D20+D22+D23+B26</f>
-        <v>51287.0700172094</v>
+        <f>D19+D22+D23+B26</f>
+        <v>51412.139599409405</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -1674,7 +1676,7 @@
       <c r="G37" s="15"/>
       <c r="I37" s="15">
         <f>I34-I35</f>
-        <v>1065.6008286415963</v>
+        <v>1079.5394454415873</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -1704,7 +1706,7 @@
       <c r="G38" s="15"/>
       <c r="I38" s="15">
         <f>I37*7.78</f>
-        <v>8290.3744468316199</v>
+        <v>8398.8168855355489</v>
       </c>
       <c r="J38" s="37"/>
     </row>
@@ -1740,7 +1742,7 @@
       <c r="G40" s="32"/>
       <c r="I40" s="16">
         <f>(I37/I35)</f>
-        <v>2.077718279254466E-2</v>
+        <v>2.0997753718345315E-2</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -1767,7 +1769,7 @@
       <c r="G42" s="34"/>
       <c r="I42" s="38">
         <f>(I34-E34)/I35</f>
-        <v>0.4043106934923959</v>
+        <v>0.40603093369587745</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
@@ -1796,7 +1798,7 @@
       <c r="G44" s="34"/>
       <c r="I44" s="44">
         <f>(I34-B34)/I34</f>
-        <v>0.56824781554022008</v>
+        <v>0.56939117949176732</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">

--- a/Portfolio.xlsx
+++ b/Portfolio.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\john.hcpang\Documents\Practice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF1D40DF-39C4-4A99-BFCE-B6D0135782D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F70CFC35-DF6C-4B1E-8FC4-EF364ED35EB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{E7CDDCE8-D664-4969-9A02-FA9A05E60C5E}"/>
   </bookViews>
@@ -125,9 +125,6 @@
     <t>IBM</t>
   </si>
   <si>
-    <t>IREN</t>
-  </si>
-  <si>
     <t>NOK</t>
   </si>
   <si>
@@ -155,9 +152,6 @@
     <t>CRCL</t>
   </si>
   <si>
-    <t>SGOV</t>
-  </si>
-  <si>
     <t>DRAM</t>
   </si>
   <si>
@@ -179,7 +173,13 @@
     <t>Ibkr</t>
   </si>
   <si>
-    <t>RAM</t>
+    <t>SGOV(in ib)</t>
+  </si>
+  <si>
+    <t>SGOV(in webull)</t>
+  </si>
+  <si>
+    <t>VSH</t>
   </si>
 </sst>
 </file>
@@ -230,7 +230,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -273,8 +273,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -323,13 +329,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -442,13 +459,29 @@
     <xf numFmtId="167" fontId="2" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="5" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="2" builtinId="4"/>
@@ -823,11 +856,11 @@
         <v>15</v>
       </c>
       <c r="G1" s="34"/>
-      <c r="H1" s="47" t="s">
-        <v>43</v>
-      </c>
-      <c r="I1" s="49" t="s">
-        <v>44</v>
+      <c r="H1" s="46" t="s">
+        <v>41</v>
+      </c>
+      <c r="I1" s="48" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:121" x14ac:dyDescent="0.25">
@@ -841,15 +874,15 @@
         <v>731.12090000000001</v>
       </c>
       <c r="D2" s="15">
-        <f>C2*B2</f>
+        <f t="shared" ref="D2:D7" si="0">C2*B2</f>
         <v>4701.25361118</v>
       </c>
       <c r="E2" s="17">
-        <f>D2/($D$19+$D$22+$D$23+$B$27+$B$26)</f>
-        <v>9.1256904271929298E-2</v>
-      </c>
-      <c r="G2" s="46" t="s">
-        <v>42</v>
+        <f t="shared" ref="E2:E18" si="1">D2/($D$19+$D$22+$D$23+$B$27+$B$26)</f>
+        <v>9.1391694480095181E-2</v>
+      </c>
+      <c r="G2" s="45" t="s">
+        <v>40</v>
       </c>
       <c r="H2" s="39">
         <v>301750</v>
@@ -861,28 +894,28 @@
     </row>
     <row r="3" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B3" s="5">
-        <v>936.01310000000001</v>
+        <v>974.01310000000001</v>
       </c>
       <c r="C3" s="18">
-        <v>18.530999999999999</v>
+        <v>18.533000000000001</v>
       </c>
       <c r="D3" s="19">
-        <f>C3*B3</f>
-        <v>17345.2587561</v>
+        <f t="shared" si="0"/>
+        <v>18051.3847823</v>
       </c>
       <c r="E3" s="17">
-        <f>D3/($D$19+$D$22+$D$23+$B$27+$B$26)</f>
-        <v>0.33669202914581003</v>
-      </c>
-      <c r="G3" s="46" t="s">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>0.35091632560374036</v>
+      </c>
+      <c r="G3" s="45" t="s">
+        <v>43</v>
       </c>
       <c r="H3" s="39">
-        <f>8000+5000+8000+45000+136000</f>
-        <v>202000</v>
+        <f>8000+5000+8000+45000+136000+8000</f>
+        <v>210000</v>
       </c>
       <c r="I3" s="39">
         <v>0</v>
@@ -890,7 +923,7 @@
     </row>
     <row r="4" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B4" s="34">
         <v>3.1</v>
@@ -899,12 +932,12 @@
         <v>431.11099999999999</v>
       </c>
       <c r="D4" s="19">
-        <f>C4*B4</f>
+        <f t="shared" si="0"/>
         <v>1336.4440999999999</v>
       </c>
       <c r="E4" s="17">
-        <f>D4/($D$19+$D$22+$D$23+$B$27+$B$26)</f>
-        <v>2.5941963864373013E-2</v>
+        <f t="shared" si="1"/>
+        <v>2.5980281214029004E-2</v>
       </c>
       <c r="G4" s="33"/>
       <c r="H4" s="33"/>
@@ -913,70 +946,60 @@
       <c r="K4" s="33"/>
     </row>
     <row r="5" spans="1:121" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" s="5">
-        <v>3</v>
-      </c>
-      <c r="C5" s="18">
-        <v>660.56</v>
-      </c>
-      <c r="D5" s="40">
-        <f>C5*B5</f>
-        <v>1981.6799999999998</v>
+      <c r="A5" s="49" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5">
+        <v>9</v>
+      </c>
+      <c r="C5">
+        <v>100.446</v>
+      </c>
+      <c r="D5" s="19">
+        <f t="shared" si="0"/>
+        <v>904.01400000000001</v>
       </c>
       <c r="E5" s="17">
-        <f>D5/($D$19+$D$22+$D$23+$B$27+$B$26)</f>
-        <v>3.8466757383081501E-2</v>
-      </c>
-      <c r="G5" s="33"/>
-      <c r="H5" s="33"/>
-      <c r="I5"/>
-      <c r="J5" s="33"/>
-      <c r="K5" s="33"/>
+        <f t="shared" si="1"/>
+        <v>1.7573902224132843E-2</v>
+      </c>
     </row>
     <row r="6" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="B6" s="5">
-        <v>6</v>
-      </c>
-      <c r="C6" s="14">
-        <v>301.79500000000002</v>
-      </c>
-      <c r="D6" s="15">
-        <f t="shared" ref="D6:D7" si="0">C6*B6</f>
-        <v>1810.77</v>
+        <v>24.005400000000002</v>
+      </c>
+      <c r="C6" s="18">
+        <v>100.63</v>
+      </c>
+      <c r="D6" s="19">
+        <f t="shared" si="0"/>
+        <v>2415.6634020000001</v>
       </c>
       <c r="E6" s="17">
-        <f>D6/($D$19+$D$22+$D$23+$B$27+$B$26)</f>
-        <v>3.5149191729523688E-2</v>
-      </c>
-      <c r="G6" s="33"/>
-      <c r="H6" s="33"/>
-      <c r="I6"/>
-      <c r="J6" s="33"/>
-      <c r="K6" s="33"/>
+        <f t="shared" ref="E6:E15" si="2">D6/($D$19+$D$22+$D$23+$B$27+$B$26)</f>
+        <v>4.6960149326408789E-2</v>
+      </c>
     </row>
     <row r="7" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B7" s="5">
-        <v>15</v>
+        <v>4.9870999999999999</v>
       </c>
       <c r="C7" s="18">
-        <v>71.781999999999996</v>
-      </c>
-      <c r="D7" s="39">
+        <v>638.44000000000005</v>
+      </c>
+      <c r="D7" s="40">
         <f t="shared" si="0"/>
-        <v>1076.73</v>
+        <v>3183.9641240000001</v>
       </c>
       <c r="E7" s="17">
-        <f>D7/($D$19+$D$22+$D$23+$B$27+$B$26)</f>
-        <v>2.0900605383858822E-2</v>
+        <f t="shared" si="2"/>
+        <v>6.1895804932581552E-2</v>
       </c>
       <c r="G7" s="33"/>
       <c r="H7" s="33"/>
@@ -986,21 +1009,21 @@
     </row>
     <row r="8" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B8" s="5">
-        <v>180</v>
-      </c>
-      <c r="C8" s="18">
-        <v>16.021000000000001</v>
-      </c>
-      <c r="D8" s="40">
-        <f>B8*C8</f>
-        <v>2883.78</v>
+        <v>6</v>
+      </c>
+      <c r="C8" s="14">
+        <v>301.79500000000002</v>
+      </c>
+      <c r="D8" s="15">
+        <f t="shared" ref="D8:D9" si="3">C8*B8</f>
+        <v>1810.77</v>
       </c>
       <c r="E8" s="17">
-        <f>D8/($D$19+$D$22+$D$23+$B$27+$B$26)</f>
-        <v>5.5977587504633837E-2</v>
+        <f t="shared" si="2"/>
+        <v>3.5201108534152155E-2</v>
       </c>
       <c r="G8" s="33"/>
       <c r="H8" s="33"/>
@@ -1010,41 +1033,41 @@
     </row>
     <row r="9" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B9" s="5">
-        <v>17</v>
-      </c>
-      <c r="C9" s="14">
-        <v>401.18400000000003</v>
-      </c>
-      <c r="D9" s="15">
-        <f>C9*B9</f>
-        <v>6820.1280000000006</v>
+        <v>15</v>
+      </c>
+      <c r="C9" s="18">
+        <v>71.781999999999996</v>
+      </c>
+      <c r="D9" s="39">
+        <f t="shared" si="3"/>
+        <v>1076.73</v>
       </c>
       <c r="E9" s="17">
-        <f>D9/($D$19+$D$22+$D$23+$B$27+$B$26)</f>
-        <v>0.1323867673375928</v>
+        <f t="shared" si="2"/>
+        <v>2.0931476439292485E-2</v>
       </c>
       <c r="M9" s="37"/>
     </row>
     <row r="10" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="B10" s="5">
-        <v>9</v>
+        <v>185</v>
       </c>
       <c r="C10" s="18">
-        <v>93.789000000000001</v>
-      </c>
-      <c r="D10" s="19">
-        <f t="shared" ref="D10:D18" si="1">C10*B10</f>
-        <v>844.101</v>
+        <v>15.927</v>
+      </c>
+      <c r="D10" s="40">
+        <f>B10*C10</f>
+        <v>2946.4949999999999</v>
       </c>
       <c r="E10" s="17">
-        <f>D10/($D$19+$D$22+$D$23+$B$27+$B$26)</f>
-        <v>1.6385000794182956E-2</v>
+        <f t="shared" si="2"/>
+        <v>5.7279439293967019E-2</v>
       </c>
       <c r="G10" s="33"/>
       <c r="H10" s="33"/>
@@ -1054,21 +1077,21 @@
     </row>
     <row r="11" spans="1:121" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" s="5">
-        <v>3.6</v>
-      </c>
-      <c r="C11" s="18">
-        <v>181.05799999999999</v>
-      </c>
-      <c r="D11" s="19">
-        <f t="shared" si="1"/>
-        <v>651.80880000000002</v>
+        <v>18</v>
+      </c>
+      <c r="C11" s="14">
+        <v>399.46600000000001</v>
+      </c>
+      <c r="D11" s="15">
+        <f t="shared" ref="D11:D18" si="4">C11*B11</f>
+        <v>7190.3879999999999</v>
       </c>
       <c r="E11" s="17">
-        <f>D11/($D$19+$D$22+$D$23+$B$27+$B$26)</f>
-        <v>1.2652381297564439E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.13978010923014259</v>
       </c>
       <c r="F11"/>
       <c r="G11" s="33"/>
@@ -1189,21 +1212,21 @@
     </row>
     <row r="12" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B12" s="5">
         <v>10</v>
       </c>
       <c r="C12" s="18">
-        <v>62.938000000000002</v>
-      </c>
-      <c r="D12" s="40">
-        <f t="shared" si="1"/>
-        <v>629.38</v>
+        <v>91.68</v>
+      </c>
+      <c r="D12" s="19">
+        <f t="shared" si="4"/>
+        <v>916.80000000000007</v>
       </c>
       <c r="E12" s="17">
-        <f>D12/($D$19+$D$22+$D$23+$B$27+$B$26)</f>
-        <v>1.2217011708128375E-2</v>
+        <f t="shared" si="2"/>
+        <v>1.7822460226373699E-2</v>
       </c>
       <c r="J12" s="33"/>
       <c r="K12" s="33"/>
@@ -1211,21 +1234,21 @@
     </row>
     <row r="13" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B13" s="5">
-        <v>1</v>
+        <v>5.6</v>
       </c>
       <c r="C13" s="18">
-        <v>0</v>
+        <v>196.43199999999999</v>
       </c>
       <c r="D13" s="19">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>1100.0192</v>
       </c>
       <c r="E13" s="17">
-        <f>D13/($D$19+$D$22+$D$23+$B$27+$B$26)</f>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>2.138421513988592E-2</v>
       </c>
       <c r="J13" s="33"/>
       <c r="K13" s="33"/>
@@ -1233,21 +1256,21 @@
     </row>
     <row r="14" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B14" s="5">
         <v>1</v>
       </c>
       <c r="C14" s="18">
-        <v>210.02</v>
+        <v>0</v>
       </c>
       <c r="D14" s="19">
-        <f t="shared" si="1"/>
-        <v>210.02</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="E14" s="17">
-        <f>D14/($D$19+$D$22+$D$23+$B$27+$B$26)</f>
-        <v>4.076737104676223E-3</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="J14" s="33"/>
       <c r="K14" s="33"/>
@@ -1255,21 +1278,21 @@
     </row>
     <row r="15" spans="1:121" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B15" s="5">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C15" s="18">
-        <v>287.54899999999998</v>
-      </c>
-      <c r="D15" s="40">
-        <f>C15*B15</f>
-        <v>3450.5879999999997</v>
+        <v>210.02</v>
+      </c>
+      <c r="D15" s="19">
+        <f t="shared" si="4"/>
+        <v>210.02</v>
       </c>
       <c r="E15" s="17">
-        <f>D15/($D$19+$D$22+$D$23+$B$27+$B$26)</f>
-        <v>6.6980002535713346E-2</v>
+        <f t="shared" si="2"/>
+        <v>4.0827586133758767E-3</v>
       </c>
       <c r="G15" s="33"/>
       <c r="H15" s="33"/>
@@ -1280,7 +1303,7 @@
     </row>
     <row r="16" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B16" s="5">
         <v>8</v>
@@ -1289,34 +1312,34 @@
         <v>80.599999999999994</v>
       </c>
       <c r="D16" s="19">
-        <f>C16*B16</f>
+        <f t="shared" si="4"/>
         <v>644.79999999999995</v>
       </c>
       <c r="E16" s="17">
-        <f>D16/($D$19+$D$22+$D$23+$B$27+$B$26)</f>
-        <v>1.2516332183102696E-2</v>
+        <f t="shared" si="1"/>
+        <v>1.2534819321515881E-2</v>
       </c>
       <c r="J16" s="33"/>
       <c r="K16" s="33"/>
       <c r="L16" s="33"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17" s="5">
-        <v>23</v>
-      </c>
-      <c r="C17" s="18">
-        <v>100.62</v>
-      </c>
-      <c r="D17" s="19">
+      <c r="A17" s="49" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" s="50">
+        <v>7</v>
+      </c>
+      <c r="C17" s="51">
+        <v>284.97699999999998</v>
+      </c>
+      <c r="D17" s="52">
+        <f t="shared" si="4"/>
+        <v>1994.8389999999999</v>
+      </c>
+      <c r="E17" s="53">
         <f t="shared" si="1"/>
-        <v>2314.2600000000002</v>
-      </c>
-      <c r="E17" s="17">
-        <f>D17/($D$19+$D$22+$D$23+$B$27+$B$26)</f>
-        <v>4.4922529339434324E-2</v>
+        <v>3.8779383437520812E-2</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
@@ -1324,24 +1347,24 @@
         <v>46</v>
       </c>
       <c r="B18" s="5">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C18" s="18">
-        <v>29.497</v>
+        <v>48.87</v>
       </c>
       <c r="D18" s="19">
+        <f t="shared" si="4"/>
+        <v>48.87</v>
+      </c>
+      <c r="E18" s="54">
         <f t="shared" si="1"/>
-        <v>855.41300000000001</v>
-      </c>
-      <c r="E18" s="50">
-        <f>D18/($D$19+$D$22+$D$23+$B$27+$B$26)</f>
-        <v>1.6604580120571383E-2</v>
+        <v>9.5002577581029942E-4</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D19" s="20">
         <f>SUM(D2:D18)</f>
-        <v>47556.415267280005</v>
+        <v>48532.455219480005</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
@@ -1388,9 +1411,9 @@
       </c>
       <c r="E22" s="16">
         <f>D22/(D19+D22+D23+B26+B72)</f>
-        <v>1.9015765547727381E-2</v>
-      </c>
-      <c r="H22" s="48"/>
+        <v>1.9025001984153092E-2</v>
+      </c>
+      <c r="H22" s="47"/>
       <c r="J22" s="33"/>
       <c r="K22" s="33"/>
       <c r="L22" s="33"/>
@@ -1411,7 +1434,7 @@
       </c>
       <c r="E23" s="16">
         <f>D23/(D19+D22+D23+B26+B27)</f>
-        <v>7.3002194458611225E-3</v>
+        <v>7.3110021708134411E-3</v>
       </c>
       <c r="J23" s="33"/>
       <c r="K23" s="33"/>
@@ -1437,14 +1460,14 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B26" s="7">
-        <v>2502</v>
+        <v>1501</v>
       </c>
       <c r="C26" s="43">
         <f>B26/(D19+B27)</f>
-        <v>5.2495789499203908E-2</v>
+        <v>3.089368247282533E-2</v>
       </c>
       <c r="D26" s="26"/>
       <c r="E26" s="12"/>
@@ -1454,14 +1477,14 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B27" s="7">
-        <v>104.55</v>
+        <v>53.53</v>
       </c>
       <c r="C27" s="43">
         <f>B27/D19</f>
-        <v>2.1984415648740666E-3</v>
+        <v>1.1029732528041168E-3</v>
       </c>
       <c r="D27" s="26"/>
       <c r="E27" s="12"/>
@@ -1490,7 +1513,7 @@
         <v>46184</v>
       </c>
       <c r="G29" s="27">
-        <v>46207</v>
+        <v>46210</v>
       </c>
       <c r="I29" s="20" t="s">
         <v>20</v>
@@ -1517,16 +1540,18 @@
       <c r="F30" s="15">
         <v>21348.19</v>
       </c>
-      <c r="G30" s="15"/>
+      <c r="G30" s="15">
+        <v>21287.19</v>
+      </c>
       <c r="I30" s="15">
-        <v>21940.62</v>
+        <v>21287.19</v>
       </c>
       <c r="J30" s="33"/>
       <c r="K30" s="33"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="10" t="s">
-        <v>36</v>
+    <row r="31" spans="1:12" s="33" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="55" t="s">
+        <v>35</v>
       </c>
       <c r="B31" s="28">
         <v>141.21</v>
@@ -1543,12 +1568,12 @@
       <c r="F31" s="15">
         <v>6141.14</v>
       </c>
-      <c r="G31" s="15"/>
+      <c r="G31" s="15">
+        <v>30268.1</v>
+      </c>
       <c r="I31" s="15">
-        <v>29339</v>
-      </c>
-      <c r="J31" s="33"/>
-      <c r="K31" s="33"/>
+        <v>30268.1</v>
+      </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="29" t="s">
@@ -1569,10 +1594,12 @@
       <c r="F32" s="15">
         <v>1014.79742</v>
       </c>
-      <c r="G32" s="15"/>
+      <c r="G32" s="15">
+        <v>1164.81</v>
+      </c>
       <c r="I32" s="15">
-        <f>66511.1*B23+66511.1*B22</f>
-        <v>1212.0590448510002</v>
+        <f>63918.36*B23+63918.36*B22</f>
+        <v>1164.8104808076</v>
       </c>
       <c r="J32" s="33"/>
       <c r="K32" s="33"/>
@@ -1608,10 +1635,12 @@
       <c r="F34" s="15">
         <v>28504.13</v>
       </c>
-      <c r="G34" s="15"/>
+      <c r="G34" s="15">
+        <v>52720.1</v>
+      </c>
       <c r="I34" s="35">
         <f>SUM(I30:I32)</f>
-        <v>52491.679044850993</v>
+        <v>52720.100480807596</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -1633,11 +1662,13 @@
       <c r="F35" s="15">
         <v>28277.200000000001</v>
       </c>
-      <c r="G35" s="15"/>
+      <c r="G35" s="15">
+        <v>51387.18</v>
+      </c>
       <c r="H35" s="9"/>
       <c r="I35" s="15">
         <f>D19+D22+D23+B26</f>
-        <v>51412.139599409405</v>
+        <v>51387.179551609399</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -1654,29 +1685,32 @@
         <v>11</v>
       </c>
       <c r="B37" s="30">
-        <f>B34-B35</f>
+        <f t="shared" ref="B37:G37" si="5">B34-B35</f>
         <v>2020.8500000000022</v>
       </c>
       <c r="C37" s="15">
-        <f>C34-C35</f>
+        <f t="shared" si="5"/>
         <v>3260.630000000001</v>
       </c>
       <c r="D37" s="15">
-        <f>D34-D35</f>
+        <f t="shared" si="5"/>
         <v>2350.5800000000017</v>
       </c>
       <c r="E37" s="15">
-        <f>E34-E35</f>
+        <f t="shared" si="5"/>
         <v>4382.239999999998</v>
       </c>
       <c r="F37" s="15">
-        <f>F34-F35</f>
+        <f t="shared" si="5"/>
         <v>226.93000000000029</v>
       </c>
-      <c r="G37" s="15"/>
+      <c r="G37" s="15">
+        <f t="shared" si="5"/>
+        <v>1332.9199999999983</v>
+      </c>
       <c r="I37" s="15">
         <f>I34-I35</f>
-        <v>1079.5394454415873</v>
+        <v>1332.920929198197</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -1703,10 +1737,13 @@
         <f>F37*7.8</f>
         <v>1770.0540000000021</v>
       </c>
-      <c r="G38" s="15"/>
+      <c r="G38" s="15">
+        <f>G37*7.8</f>
+        <v>10396.775999999985</v>
+      </c>
       <c r="I38" s="15">
         <f>I37*7.78</f>
-        <v>8398.8168855355489</v>
+        <v>10370.124829161972</v>
       </c>
       <c r="J38" s="37"/>
     </row>
@@ -1739,15 +1776,18 @@
         <f>(F37/F35)</f>
         <v>8.0251934420664094E-3</v>
       </c>
-      <c r="G40" s="32"/>
+      <c r="G40" s="32">
+        <f>(G37/G35)</f>
+        <v>2.5938765271805112E-2</v>
+      </c>
       <c r="I40" s="16">
         <f>(I37/I35)</f>
-        <v>2.0997753718345315E-2</v>
+        <v>2.5938783580435894E-2</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B42" s="34"/>
       <c r="C42" s="38">
@@ -1766,39 +1806,43 @@
         <f>(F34-E34)/E35</f>
         <v>-0.11428987916805573</v>
       </c>
-      <c r="G42" s="34"/>
-      <c r="I42" s="38">
-        <f>(I34-E34)/I35</f>
-        <v>0.40603093369587745</v>
-      </c>
+      <c r="G42" s="38">
+        <f>(G34-F34)/F35</f>
+        <v>0.85637792992234019</v>
+      </c>
+      <c r="I42" s="56"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" s="45" t="s">
-        <v>30</v>
+      <c r="A44" s="44" t="s">
+        <v>29</v>
       </c>
       <c r="B44" s="34">
         <v>0</v>
       </c>
       <c r="C44" s="38">
-        <f>(C34-B34)/B35</f>
-        <v>0.20401913661731574</v>
+        <f>(C34-$B$34)/$B$34</f>
+        <v>0.18577885254329218</v>
       </c>
       <c r="D44" s="38">
-        <f>(D34-B34)/D34</f>
-        <v>0.22127368860221955</v>
+        <f t="shared" ref="D44:I44" si="6">(D34-$B$34)/$B$34</f>
+        <v>0.2841482114621795</v>
       </c>
       <c r="E44" s="38">
-        <f>(E34-B34)/E34</f>
-        <v>0.28508234240320635</v>
+        <f t="shared" si="6"/>
+        <v>0.39876248596448838</v>
       </c>
       <c r="F44" s="38">
-        <f>(F34-B34)/F34</f>
-        <v>0.20701386079841763</v>
-      </c>
-      <c r="G44" s="34"/>
-      <c r="I44" s="44">
-        <f>(I34-B34)/I34</f>
-        <v>0.56939117949176732</v>
+        <f t="shared" si="6"/>
+        <v>0.26105608984143081</v>
+      </c>
+      <c r="G44" s="38">
+        <f t="shared" si="6"/>
+        <v>1.3323989598015871</v>
+      </c>
+      <c r="H44" s="56"/>
+      <c r="I44" s="38">
+        <f t="shared" si="6"/>
+        <v>1.3323989810730781</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">

--- a/Portfolio.xlsx
+++ b/Portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\john.hcpang\Documents\Practice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F70CFC35-DF6C-4B1E-8FC4-EF364ED35EB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2501A451-D3DD-4D61-A6D3-2079460483F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{E7CDDCE8-D664-4969-9A02-FA9A05E60C5E}"/>
   </bookViews>
@@ -476,12 +476,12 @@
     <xf numFmtId="44" fontId="2" fillId="0" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="2" fillId="5" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="0" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="2" builtinId="4"/>
@@ -1337,7 +1337,7 @@
         <f t="shared" si="4"/>
         <v>1994.8389999999999</v>
       </c>
-      <c r="E17" s="53">
+      <c r="E17" s="55">
         <f t="shared" si="1"/>
         <v>3.8779383437520812E-2</v>
       </c>
@@ -1356,7 +1356,7 @@
         <f t="shared" si="4"/>
         <v>48.87</v>
       </c>
-      <c r="E18" s="54">
+      <c r="E18" s="56">
         <f t="shared" si="1"/>
         <v>9.5002577581029942E-4</v>
       </c>
@@ -1544,13 +1544,13 @@
         <v>21287.19</v>
       </c>
       <c r="I30" s="15">
-        <v>21287.19</v>
+        <v>21104.43</v>
       </c>
       <c r="J30" s="33"/>
       <c r="K30" s="33"/>
     </row>
     <row r="31" spans="1:12" s="33" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="55" t="s">
+      <c r="A31" s="53" t="s">
         <v>35</v>
       </c>
       <c r="B31" s="28">
@@ -1572,7 +1572,7 @@
         <v>30268.1</v>
       </c>
       <c r="I31" s="15">
-        <v>30268.1</v>
+        <v>29925</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
@@ -1598,8 +1598,8 @@
         <v>1164.81</v>
       </c>
       <c r="I32" s="15">
-        <f>63918.36*B23+63918.36*B22</f>
-        <v>1164.8104808076</v>
+        <f>62537.97*B23+62537.97*B22</f>
+        <v>1139.6550678777</v>
       </c>
       <c r="J32" s="33"/>
       <c r="K32" s="33"/>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="I34" s="35">
         <f>SUM(I30:I32)</f>
-        <v>52720.100480807596</v>
+        <v>52169.085067877699</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="I37" s="15">
         <f>I34-I35</f>
-        <v>1332.920929198197</v>
+        <v>781.90551626829983</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -1742,8 +1742,8 @@
         <v>10396.775999999985</v>
       </c>
       <c r="I38" s="15">
-        <f>I37*7.78</f>
-        <v>10370.124829161972</v>
+        <f>I37*7.8</f>
+        <v>6098.8630268927382</v>
       </c>
       <c r="J38" s="37"/>
     </row>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I40" s="16">
         <f>(I37/I35)</f>
-        <v>2.5938783580435894E-2</v>
+        <v>1.5215964820233284E-2</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -1810,7 +1810,7 @@
         <f>(G34-F34)/F35</f>
         <v>0.85637792992234019</v>
       </c>
-      <c r="I42" s="56"/>
+      <c r="I42" s="54"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="44" t="s">
@@ -1839,10 +1839,10 @@
         <f t="shared" si="6"/>
         <v>1.3323989598015871</v>
       </c>
-      <c r="H44" s="56"/>
+      <c r="H44" s="54"/>
       <c r="I44" s="38">
         <f t="shared" si="6"/>
-        <v>1.3323989810730781</v>
+        <v>1.3080214139601112</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">

--- a/Portfolio.xlsx
+++ b/Portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\john.hcpang\Documents\Practice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2501A451-D3DD-4D61-A6D3-2079460483F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{848F57F7-3B72-4DF8-8E59-EBF6FDF7FCFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{E7CDDCE8-D664-4969-9A02-FA9A05E60C5E}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Portfolio" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Portfolio!$E$1:$E$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Portfolio!$E$1:$E$22</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="48">
   <si>
     <t>Shares</t>
   </si>
@@ -180,6 +180,9 @@
   </si>
   <si>
     <t>VSH</t>
+  </si>
+  <si>
+    <t>CEG</t>
   </si>
 </sst>
 </file>
@@ -346,7 +349,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -467,20 +470,10 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="44" fontId="2" fillId="5" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="0" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
@@ -878,8 +871,8 @@
         <v>4701.25361118</v>
       </c>
       <c r="E2" s="17">
-        <f t="shared" ref="E2:E18" si="1">D2/($D$19+$D$22+$D$23+$B$27+$B$26)</f>
-        <v>9.1391694480095181E-2</v>
+        <f t="shared" ref="E2:E19" si="1">D2/($D$20+$D$24+$D$25+$B$29+$B$28)</f>
+        <v>9.1358959155294475E-2</v>
       </c>
       <c r="G2" s="45" t="s">
         <v>40</v>
@@ -908,7 +901,7 @@
       </c>
       <c r="E3" s="17">
         <f t="shared" si="1"/>
-        <v>0.35091632560374036</v>
+        <v>0.3507906319073727</v>
       </c>
       <c r="G3" s="45" t="s">
         <v>43</v>
@@ -937,7 +930,7 @@
       </c>
       <c r="E4" s="17">
         <f t="shared" si="1"/>
-        <v>2.5980281214029004E-2</v>
+        <v>2.5970975412787513E-2</v>
       </c>
       <c r="G4" s="33"/>
       <c r="H4" s="33"/>
@@ -950,18 +943,18 @@
         <v>45</v>
       </c>
       <c r="B5">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C5">
         <v>100.446</v>
       </c>
       <c r="D5" s="19">
         <f t="shared" si="0"/>
-        <v>904.01400000000001</v>
+        <v>602.67599999999993</v>
       </c>
       <c r="E5" s="17">
         <f t="shared" si="1"/>
-        <v>1.7573902224132843E-2</v>
+        <v>1.1711738319528011E-2</v>
       </c>
     </row>
     <row r="6" spans="1:121" x14ac:dyDescent="0.25">
@@ -979,8 +972,8 @@
         <v>2415.6634020000001</v>
       </c>
       <c r="E6" s="17">
-        <f t="shared" ref="E6:E15" si="2">D6/($D$19+$D$22+$D$23+$B$27+$B$26)</f>
-        <v>4.6960149326408789E-2</v>
+        <f t="shared" si="1"/>
+        <v>4.6943328807327329E-2</v>
       </c>
     </row>
     <row r="7" spans="1:121" x14ac:dyDescent="0.25">
@@ -998,8 +991,8 @@
         <v>3183.9641240000001</v>
       </c>
       <c r="E7" s="17">
-        <f t="shared" si="2"/>
-        <v>6.1895804932581552E-2</v>
+        <f t="shared" si="1"/>
+        <v>6.1873634654529538E-2</v>
       </c>
       <c r="G7" s="33"/>
       <c r="H7" s="33"/>
@@ -1018,12 +1011,12 @@
         <v>301.79500000000002</v>
       </c>
       <c r="D8" s="15">
-        <f t="shared" ref="D8:D9" si="3">C8*B8</f>
+        <f t="shared" ref="D8:D9" si="2">C8*B8</f>
         <v>1810.77</v>
       </c>
       <c r="E8" s="17">
-        <f t="shared" si="2"/>
-        <v>3.5201108534152155E-2</v>
+        <f t="shared" si="1"/>
+        <v>3.5188499951635276E-2</v>
       </c>
       <c r="G8" s="33"/>
       <c r="H8" s="33"/>
@@ -1042,12 +1035,12 @@
         <v>71.781999999999996</v>
       </c>
       <c r="D9" s="39">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>1076.73</v>
       </c>
       <c r="E9" s="17">
-        <f t="shared" si="2"/>
-        <v>2.0931476439292485E-2</v>
+        <f t="shared" si="1"/>
+        <v>2.0923979054724921E-2</v>
       </c>
       <c r="M9" s="37"/>
     </row>
@@ -1066,8 +1059,8 @@
         <v>2946.4949999999999</v>
       </c>
       <c r="E10" s="17">
-        <f t="shared" si="2"/>
-        <v>5.7279439293967019E-2</v>
+        <f t="shared" si="1"/>
+        <v>5.7258922538474553E-2</v>
       </c>
       <c r="G10" s="33"/>
       <c r="H10" s="33"/>
@@ -1086,12 +1079,12 @@
         <v>399.46600000000001</v>
       </c>
       <c r="D11" s="15">
-        <f t="shared" ref="D11:D18" si="4">C11*B11</f>
+        <f t="shared" ref="D11:D18" si="3">C11*B11</f>
         <v>7190.3879999999999</v>
       </c>
       <c r="E11" s="17">
-        <f t="shared" si="2"/>
-        <v>0.13978010923014259</v>
+        <f t="shared" si="1"/>
+        <v>0.13973004180002918</v>
       </c>
       <c r="F11"/>
       <c r="G11" s="33"/>
@@ -1221,12 +1214,12 @@
         <v>91.68</v>
       </c>
       <c r="D12" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>916.80000000000007</v>
       </c>
       <c r="E12" s="17">
-        <f t="shared" si="2"/>
-        <v>1.7822460226373699E-2</v>
+        <f t="shared" si="1"/>
+        <v>1.7816076451266157E-2</v>
       </c>
       <c r="J12" s="33"/>
       <c r="K12" s="33"/>
@@ -1243,12 +1236,12 @@
         <v>196.43199999999999</v>
       </c>
       <c r="D13" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1100.0192</v>
       </c>
       <c r="E13" s="17">
-        <f t="shared" si="2"/>
-        <v>2.138421513988592E-2</v>
+        <f t="shared" si="1"/>
+        <v>2.1376555590162126E-2</v>
       </c>
       <c r="J13" s="33"/>
       <c r="K13" s="33"/>
@@ -1265,11 +1258,11 @@
         <v>0</v>
       </c>
       <c r="D14" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E14" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J14" s="33"/>
@@ -1287,12 +1280,12 @@
         <v>210.02</v>
       </c>
       <c r="D15" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>210.02</v>
       </c>
       <c r="E15" s="17">
-        <f t="shared" si="2"/>
-        <v>4.0827586133758767E-3</v>
+        <f t="shared" si="1"/>
+        <v>4.0812962219621707E-3</v>
       </c>
       <c r="G15" s="33"/>
       <c r="H15" s="33"/>
@@ -1312,537 +1305,561 @@
         <v>80.599999999999994</v>
       </c>
       <c r="D16" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>644.79999999999995</v>
       </c>
       <c r="E16" s="17">
         <f t="shared" si="1"/>
-        <v>1.2534819321515881E-2</v>
+        <v>1.2530329511099931E-2</v>
       </c>
       <c r="J16" s="33"/>
       <c r="K16" s="33"/>
       <c r="L16" s="33"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="49" t="s">
+      <c r="A17" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B17" s="50">
+      <c r="B17" s="5">
         <v>7</v>
       </c>
-      <c r="C17" s="51">
+      <c r="C17" s="18">
         <v>284.97699999999998</v>
       </c>
-      <c r="D17" s="52">
-        <f t="shared" si="4"/>
+      <c r="D17" s="19">
+        <f t="shared" si="3"/>
         <v>1994.8389999999999</v>
       </c>
-      <c r="E17" s="55">
+      <c r="E17" s="52">
         <f t="shared" si="1"/>
-        <v>3.8779383437520812E-2</v>
+        <v>3.8765493163140631E-2</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B18" s="5">
         <v>1</v>
       </c>
       <c r="C18" s="18">
+        <v>249.38</v>
+      </c>
+      <c r="D18" s="19">
+        <f t="shared" si="3"/>
+        <v>249.38</v>
+      </c>
+      <c r="E18" s="52">
+        <f t="shared" si="1"/>
+        <v>4.846174896833283E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" s="5">
+        <v>1</v>
+      </c>
+      <c r="C19" s="18">
         <v>48.87</v>
       </c>
-      <c r="D18" s="19">
-        <f t="shared" si="4"/>
+      <c r="D19" s="19">
+        <f>C19*B19</f>
         <v>48.87</v>
       </c>
-      <c r="E18" s="56">
+      <c r="E19" s="52">
         <f t="shared" si="1"/>
-        <v>9.5002577581029942E-4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D19" s="20">
-        <f>SUM(D2:D18)</f>
-        <v>48532.455219480005</v>
+        <v>9.4968548884530649E-4</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="41" t="s">
-        <v>8</v>
-      </c>
-      <c r="B20" s="42"/>
-      <c r="C20" s="42"/>
-      <c r="E20" s="34"/>
+      <c r="D20" s="20">
+        <f>SUM(D2:D19)</f>
+        <v>48480.497219480007</v>
+      </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="B21" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="D21" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>15</v>
-      </c>
       <c r="J21" s="33"/>
       <c r="K21" s="33"/>
       <c r="L21" s="33"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="B22" s="11">
-        <v>1.278341E-2</v>
-      </c>
-      <c r="C22" s="24">
-        <v>76477.34</v>
-      </c>
-      <c r="D22" s="24">
-        <f>C22*B22</f>
-        <v>977.64119292939995</v>
-      </c>
-      <c r="E22" s="16">
-        <f>D22/(D19+D22+D23+B26+B72)</f>
-        <v>1.9025001984153092E-2</v>
-      </c>
-      <c r="H22" s="47"/>
+      <c r="A22" s="41" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" s="42"/>
+      <c r="C22" s="42"/>
+      <c r="E22" s="34"/>
       <c r="J22" s="33"/>
       <c r="K22" s="33"/>
       <c r="L22" s="33"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="B23" s="11">
-        <v>5.4400000000000004E-3</v>
-      </c>
-      <c r="C23" s="15">
-        <v>69132.929999999993</v>
-      </c>
-      <c r="D23" s="24">
-        <f>C23*B23</f>
-        <v>376.08313920000001</v>
-      </c>
-      <c r="E23" s="16">
-        <f>D23/(D19+D22+D23+B26+B27)</f>
-        <v>7.3110021708134411E-3</v>
+      <c r="A23" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>15</v>
       </c>
       <c r="J23" s="33"/>
       <c r="K23" s="33"/>
       <c r="L23" s="33"/>
     </row>
     <row r="24" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="34" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" s="11">
+        <v>1.278341E-2</v>
+      </c>
+      <c r="C24" s="24">
+        <v>76477.34</v>
+      </c>
+      <c r="D24" s="24">
+        <f>C24*B24</f>
+        <v>977.64119292939995</v>
+      </c>
+      <c r="E24" s="16">
+        <f>D24/(D20+D24+D25+B28+B72)</f>
+        <v>1.9044257789878966E-2</v>
+      </c>
+      <c r="H24" s="47"/>
       <c r="J24" s="33"/>
       <c r="K24" s="33"/>
       <c r="L24" s="33"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B25" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" s="36" t="s">
-        <v>15</v>
-      </c>
-      <c r="D25" s="9"/>
-      <c r="E25" s="12"/>
+      <c r="A25" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" s="11">
+        <v>5.4400000000000004E-3</v>
+      </c>
+      <c r="C25" s="15">
+        <v>69132.929999999993</v>
+      </c>
+      <c r="D25" s="24">
+        <f>C25*B25</f>
+        <v>376.08313920000001</v>
+      </c>
+      <c r="E25" s="16">
+        <f>D25/(D20+D24+D25+B28+B29)</f>
+        <v>7.308383464244516E-3</v>
+      </c>
       <c r="J25" s="33"/>
       <c r="K25" s="33"/>
       <c r="L25" s="33"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="7">
-        <v>1501</v>
-      </c>
-      <c r="C26" s="43">
-        <f>B26/(D19+B27)</f>
-        <v>3.089368247282533E-2</v>
-      </c>
-      <c r="D26" s="26"/>
-      <c r="E26" s="12"/>
-      <c r="I26" s="33"/>
       <c r="J26" s="33"/>
       <c r="K26" s="33"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="7">
-        <v>53.53</v>
-      </c>
-      <c r="C27" s="43">
-        <f>B27/D19</f>
-        <v>1.1029732528041168E-3</v>
-      </c>
-      <c r="D27" s="26"/>
+      <c r="B27" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" s="9"/>
       <c r="E27" s="12"/>
-      <c r="I27" s="33"/>
       <c r="J27" s="33"/>
       <c r="K27" s="33"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="7">
+        <v>1501</v>
+      </c>
+      <c r="C28" s="43">
+        <f>B28/(D20+B29)</f>
+        <v>3.088196682252203E-2</v>
+      </c>
+      <c r="D28" s="26"/>
+      <c r="E28" s="12"/>
+      <c r="I28" s="33"/>
       <c r="J28" s="33"/>
       <c r="K28" s="33"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B29" s="27">
-        <v>46057</v>
-      </c>
-      <c r="C29" s="27">
-        <v>46086</v>
-      </c>
-      <c r="D29" s="27">
-        <v>46120</v>
-      </c>
-      <c r="E29" s="27">
-        <v>46147</v>
-      </c>
-      <c r="F29" s="27">
-        <v>46184</v>
-      </c>
-      <c r="G29" s="27">
-        <v>46210</v>
-      </c>
-      <c r="I29" s="20" t="s">
-        <v>20</v>
-      </c>
+      <c r="A29" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" s="7">
+        <v>123.92</v>
+      </c>
+      <c r="C29" s="43">
+        <f>B29/D20</f>
+        <v>2.5560793949573513E-3</v>
+      </c>
+      <c r="D29" s="26"/>
+      <c r="E29" s="12"/>
+      <c r="I29" s="33"/>
       <c r="J29" s="33"/>
       <c r="K29" s="33"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B30" s="28">
-        <v>21890.13</v>
-      </c>
-      <c r="C30" s="15">
-        <v>23571.81</v>
-      </c>
-      <c r="D30" s="15">
-        <v>24072.05</v>
-      </c>
-      <c r="E30" s="15">
-        <v>25466.12</v>
-      </c>
-      <c r="F30" s="15">
-        <v>21348.19</v>
-      </c>
-      <c r="G30" s="15">
-        <v>21287.19</v>
-      </c>
-      <c r="I30" s="15">
-        <v>21104.43</v>
-      </c>
       <c r="J30" s="33"/>
       <c r="K30" s="33"/>
     </row>
     <row r="31" spans="1:12" s="33" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="53" t="s">
-        <v>35</v>
-      </c>
-      <c r="B31" s="28">
-        <v>141.21</v>
-      </c>
-      <c r="C31" s="15">
-        <v>2536.0100000000002</v>
-      </c>
-      <c r="D31" s="15">
-        <v>4103</v>
-      </c>
-      <c r="E31" s="15">
-        <v>4994</v>
-      </c>
-      <c r="F31" s="15">
-        <v>6141.14</v>
-      </c>
-      <c r="G31" s="15">
-        <v>30268.1</v>
-      </c>
-      <c r="I31" s="15">
-        <v>29925</v>
+      <c r="A31"/>
+      <c r="B31" s="27">
+        <v>46057</v>
+      </c>
+      <c r="C31" s="27">
+        <v>46086</v>
+      </c>
+      <c r="D31" s="27">
+        <v>46120</v>
+      </c>
+      <c r="E31" s="27">
+        <v>46147</v>
+      </c>
+      <c r="F31" s="27">
+        <v>46184</v>
+      </c>
+      <c r="G31" s="27">
+        <v>46210</v>
+      </c>
+      <c r="H31"/>
+      <c r="I31" s="20" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" s="29" t="s">
-        <v>19</v>
+      <c r="A32" s="10" t="s">
+        <v>9</v>
       </c>
       <c r="B32" s="28">
-        <v>537.24</v>
+        <v>21890.13</v>
       </c>
       <c r="C32" s="15">
-        <v>694.79</v>
+        <v>23571.81</v>
       </c>
       <c r="D32" s="15">
-        <v>851.04</v>
+        <v>24072.05</v>
       </c>
       <c r="E32" s="15">
-        <v>1156.6400000000001</v>
+        <v>25466.12</v>
       </c>
       <c r="F32" s="15">
-        <v>1014.79742</v>
+        <v>21348.19</v>
       </c>
       <c r="G32" s="15">
-        <v>1164.81</v>
+        <v>21287.19</v>
       </c>
       <c r="I32" s="15">
-        <f>62537.97*B23+62537.97*B22</f>
-        <v>1139.6550678777</v>
+        <v>21166.38</v>
       </c>
       <c r="J32" s="33"/>
       <c r="K32" s="33"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="9"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="25"/>
-      <c r="D33" s="21"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-      <c r="I33" s="25"/>
+      <c r="A33" s="50" t="s">
+        <v>35</v>
+      </c>
+      <c r="B33" s="28">
+        <v>141.21</v>
+      </c>
+      <c r="C33" s="15">
+        <v>2536.0100000000002</v>
+      </c>
+      <c r="D33" s="15">
+        <v>4103</v>
+      </c>
+      <c r="E33" s="15">
+        <v>4994</v>
+      </c>
+      <c r="F33" s="15">
+        <v>6141.14</v>
+      </c>
+      <c r="G33" s="15">
+        <v>30268.1</v>
+      </c>
+      <c r="H33" s="33"/>
+      <c r="I33" s="15">
+        <v>30330.35</v>
+      </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="10" t="s">
+      <c r="A34" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="B34" s="28">
+        <v>537.24</v>
+      </c>
+      <c r="C34" s="15">
+        <v>694.79</v>
+      </c>
+      <c r="D34" s="15">
+        <v>851.04</v>
+      </c>
+      <c r="E34" s="15">
+        <v>1156.6400000000001</v>
+      </c>
+      <c r="F34" s="15">
+        <v>1014.79742</v>
+      </c>
+      <c r="G34" s="15">
+        <v>1164.81</v>
+      </c>
+      <c r="I34" s="15">
+        <f>63119.84*B25+63119.84*B24</f>
+        <v>1150.2587234544001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="9"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="25"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="9"/>
+      <c r="I35" s="25"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B34" s="28">
+      <c r="B36" s="28">
         <v>22603.38</v>
       </c>
-      <c r="C34" s="35">
-        <f>SUM(C30:C32)</f>
+      <c r="C36" s="35">
+        <f>SUM(C32:C34)</f>
         <v>26802.61</v>
       </c>
-      <c r="D34" s="35">
-        <f>SUM(D30:D32)</f>
+      <c r="D36" s="35">
+        <f>SUM(D32:D34)</f>
         <v>29026.09</v>
       </c>
-      <c r="E34" s="15">
+      <c r="E36" s="15">
         <v>31616.76</v>
       </c>
-      <c r="F34" s="15">
+      <c r="F36" s="15">
         <v>28504.13</v>
       </c>
-      <c r="G34" s="15">
+      <c r="G36" s="15">
         <v>52720.1</v>
       </c>
-      <c r="I34" s="35">
-        <f>SUM(I30:I32)</f>
-        <v>52169.085067877699</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B35" s="28">
-        <v>20582.53</v>
-      </c>
-      <c r="C35" s="15">
-        <v>23541.98</v>
-      </c>
-      <c r="D35" s="15">
-        <v>26675.51</v>
-      </c>
-      <c r="E35" s="15">
-        <v>27234.52</v>
-      </c>
-      <c r="F35" s="15">
-        <v>28277.200000000001</v>
-      </c>
-      <c r="G35" s="15">
-        <v>51387.18</v>
-      </c>
-      <c r="H35" s="9"/>
-      <c r="I35" s="15">
-        <f>D19+D22+D23+B26</f>
-        <v>51387.179551609399</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="9"/>
-      <c r="B36" s="9"/>
-      <c r="C36" s="1"/>
-      <c r="D36" s="21"/>
-      <c r="E36" s="12"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
+      <c r="I36" s="35">
+        <f>SUM(I32:I34)</f>
+        <v>52646.988723454393</v>
+      </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B37" s="28">
+        <v>20582.53</v>
+      </c>
+      <c r="C37" s="15">
+        <v>23541.98</v>
+      </c>
+      <c r="D37" s="15">
+        <v>26675.51</v>
+      </c>
+      <c r="E37" s="15">
+        <v>27234.52</v>
+      </c>
+      <c r="F37" s="15">
+        <v>28277.200000000001</v>
+      </c>
+      <c r="G37" s="15">
+        <v>51387.18</v>
+      </c>
+      <c r="H37" s="9"/>
+      <c r="I37" s="15">
+        <f>D20+D24+D25+B28+B29</f>
+        <v>51459.141551609398</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="9"/>
+      <c r="B38" s="9"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="9"/>
+      <c r="J38" s="37"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B37" s="30">
-        <f t="shared" ref="B37:G37" si="5">B34-B35</f>
+      <c r="B39" s="30">
+        <f t="shared" ref="B39:G39" si="4">B36-B37</f>
         <v>2020.8500000000022</v>
       </c>
-      <c r="C37" s="15">
-        <f t="shared" si="5"/>
+      <c r="C39" s="15">
+        <f t="shared" si="4"/>
         <v>3260.630000000001</v>
       </c>
-      <c r="D37" s="15">
-        <f t="shared" si="5"/>
+      <c r="D39" s="15">
+        <f t="shared" si="4"/>
         <v>2350.5800000000017</v>
       </c>
-      <c r="E37" s="15">
-        <f t="shared" si="5"/>
+      <c r="E39" s="15">
+        <f t="shared" si="4"/>
         <v>4382.239999999998</v>
       </c>
-      <c r="F37" s="15">
-        <f t="shared" si="5"/>
+      <c r="F39" s="15">
+        <f t="shared" si="4"/>
         <v>226.93000000000029</v>
       </c>
-      <c r="G37" s="15">
-        <f t="shared" si="5"/>
+      <c r="G39" s="15">
+        <f t="shared" si="4"/>
         <v>1332.9199999999983</v>
       </c>
-      <c r="I37" s="15">
-        <f>I34-I35</f>
-        <v>781.90551626829983</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B38" s="28">
-        <f>B37*7.783</f>
-        <v>15728.275550000018</v>
-      </c>
-      <c r="C38" s="15">
-        <f>C37*7.8</f>
-        <v>25432.914000000008</v>
-      </c>
-      <c r="D38" s="15">
-        <f>D37*7.8</f>
-        <v>18334.524000000012</v>
-      </c>
-      <c r="E38" s="15">
-        <f>E37*7.8</f>
-        <v>34181.47199999998</v>
-      </c>
-      <c r="F38" s="15">
-        <f>F37*7.8</f>
-        <v>1770.0540000000021</v>
-      </c>
-      <c r="G38" s="15">
-        <f>G37*7.8</f>
-        <v>10396.775999999985</v>
-      </c>
-      <c r="I38" s="15">
-        <f>I37*7.8</f>
-        <v>6098.8630268927382</v>
-      </c>
-      <c r="J38" s="37"/>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="9"/>
-      <c r="B39" s="9"/>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="12"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="9"/>
+      <c r="I39" s="15">
+        <f>I36-I37</f>
+        <v>1187.8471718449946</v>
+      </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B40" s="31">
-        <v>0.1012</v>
-      </c>
-      <c r="C40" s="16">
-        <v>0.14099999999999999</v>
-      </c>
-      <c r="D40" s="16">
-        <v>9.0300000000000005E-2</v>
-      </c>
-      <c r="E40" s="16">
-        <v>0.16200000000000001</v>
-      </c>
-      <c r="F40" s="32">
-        <f>(F37/F35)</f>
-        <v>8.0251934420664094E-3</v>
-      </c>
-      <c r="G40" s="32">
-        <f>(G37/G35)</f>
-        <v>2.5938765271805112E-2</v>
-      </c>
-      <c r="I40" s="16">
-        <f>(I37/I35)</f>
-        <v>1.5215964820233284E-2</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B40" s="28">
+        <f>B39*7.783</f>
+        <v>15728.275550000018</v>
+      </c>
+      <c r="C40" s="15">
+        <f>C39*7.8</f>
+        <v>25432.914000000008</v>
+      </c>
+      <c r="D40" s="15">
+        <f>D39*7.8</f>
+        <v>18334.524000000012</v>
+      </c>
+      <c r="E40" s="15">
+        <f>E39*7.8</f>
+        <v>34181.47199999998</v>
+      </c>
+      <c r="F40" s="15">
+        <f>F39*7.8</f>
+        <v>1770.0540000000021</v>
+      </c>
+      <c r="G40" s="15">
+        <f>G39*7.8</f>
+        <v>10396.775999999985</v>
+      </c>
+      <c r="I40" s="15">
+        <f>I39*7.8</f>
+        <v>9265.2079403909574</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="9"/>
+      <c r="B41" s="9"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="9"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B42" s="31">
+        <v>0.1012</v>
+      </c>
+      <c r="C42" s="16">
+        <v>0.14099999999999999</v>
+      </c>
+      <c r="D42" s="16">
+        <v>9.0300000000000005E-2</v>
+      </c>
+      <c r="E42" s="16">
+        <v>0.16200000000000001</v>
+      </c>
+      <c r="F42" s="32">
+        <f>(F39/F37)</f>
+        <v>8.0251934420664094E-3</v>
+      </c>
+      <c r="G42" s="32">
+        <f>(G39/G37)</f>
+        <v>2.5938765271805112E-2</v>
+      </c>
+      <c r="I42" s="16">
+        <f>(I39/I37)</f>
+        <v>2.3083307183694057E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B42" s="34"/>
-      <c r="C42" s="38">
-        <f>(C34-B34)/B35</f>
+      <c r="B44" s="34"/>
+      <c r="C44" s="38">
+        <f>(C36-B36)/B37</f>
         <v>0.20401913661731574</v>
       </c>
-      <c r="D42" s="38">
-        <f>(D34-C34)/C35</f>
+      <c r="D44" s="38">
+        <f>(D36-C36)/C37</f>
         <v>9.4447450894104903E-2</v>
       </c>
-      <c r="E42" s="38">
-        <f>(E34-D34)/D35</f>
+      <c r="E44" s="38">
+        <f>(E36-D36)/D37</f>
         <v>9.7117918270353529E-2</v>
       </c>
-      <c r="F42" s="38">
-        <f>(F34-E34)/E35</f>
+      <c r="F44" s="38">
+        <f>(F36-E36)/E37</f>
         <v>-0.11428987916805573</v>
       </c>
-      <c r="G42" s="38">
-        <f>(G34-F34)/F35</f>
+      <c r="G44" s="38">
+        <f>(G36-F36)/F37</f>
         <v>0.85637792992234019</v>
       </c>
-      <c r="I42" s="54"/>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" s="44" t="s">
+      <c r="I44" s="51"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="44" t="s">
         <v>29</v>
       </c>
-      <c r="B44" s="34">
+      <c r="B46" s="34">
         <v>0</v>
       </c>
-      <c r="C44" s="38">
-        <f>(C34-$B$34)/$B$34</f>
+      <c r="C46" s="38">
+        <f>(C36-$B$36)/$B$36</f>
         <v>0.18577885254329218</v>
       </c>
-      <c r="D44" s="38">
-        <f t="shared" ref="D44:I44" si="6">(D34-$B$34)/$B$34</f>
+      <c r="D46" s="38">
+        <f>(D36-$B$36)/$B$36</f>
         <v>0.2841482114621795</v>
       </c>
-      <c r="E44" s="38">
-        <f t="shared" si="6"/>
+      <c r="E46" s="38">
+        <f>(E36-$B$36)/$B$36</f>
         <v>0.39876248596448838</v>
       </c>
-      <c r="F44" s="38">
-        <f t="shared" si="6"/>
+      <c r="F46" s="38">
+        <f>(F36-$B$36)/$B$36</f>
         <v>0.26105608984143081</v>
       </c>
-      <c r="G44" s="38">
-        <f t="shared" si="6"/>
+      <c r="G46" s="38">
+        <f>(G36-$B$36)/$B$36</f>
         <v>1.3323989598015871</v>
       </c>
-      <c r="H44" s="54"/>
-      <c r="I44" s="38">
-        <f t="shared" si="6"/>
-        <v>1.3080214139601112</v>
+      <c r="H46" s="51"/>
+      <c r="I46" s="38">
+        <f>(I36-$B$36)/$B$36</f>
+        <v>1.3291644313131217</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">

--- a/Portfolio.xlsx
+++ b/Portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\john.hcpang\Documents\Practice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{848F57F7-3B72-4DF8-8E59-EBF6FDF7FCFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72B8CCB8-4538-4E32-87D3-DA702EBB90EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{E7CDDCE8-D664-4969-9A02-FA9A05E60C5E}"/>
   </bookViews>
@@ -173,9 +173,6 @@
     <t>Ibkr</t>
   </si>
   <si>
-    <t>SGOV(in ib)</t>
-  </si>
-  <si>
     <t>SGOV(in webull)</t>
   </si>
   <si>
@@ -183,6 +180,9 @@
   </si>
   <si>
     <t>CEG</t>
+  </si>
+  <si>
+    <t>IB01</t>
   </si>
 </sst>
 </file>
@@ -283,7 +283,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -295,19 +295,6 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -332,24 +319,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -410,9 +386,6 @@
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -428,16 +401,16 @@
     <xf numFmtId="14" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="4" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="4" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -456,9 +429,6 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="167" fontId="2" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -467,14 +437,14 @@
     <xf numFmtId="44" fontId="4" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="44" fontId="2" fillId="5" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="2" builtinId="4"/>
@@ -848,11 +818,11 @@
       <c r="E1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="34"/>
-      <c r="H1" s="46" t="s">
+      <c r="G1" s="33"/>
+      <c r="H1" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="I1" s="48" t="s">
+      <c r="I1" s="46" t="s">
         <v>42</v>
       </c>
     </row>
@@ -872,18 +842,18 @@
       </c>
       <c r="E2" s="17">
         <f t="shared" ref="E2:E19" si="1">D2/($D$20+$D$24+$D$25+$B$29+$B$28)</f>
-        <v>9.1358959155294475E-2</v>
-      </c>
-      <c r="G2" s="45" t="s">
+        <v>9.1625607134065701E-2</v>
+      </c>
+      <c r="G2" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="H2" s="39">
+      <c r="H2" s="38">
         <v>301750</v>
       </c>
-      <c r="I2" s="39">
+      <c r="I2" s="38">
         <v>207310</v>
       </c>
-      <c r="M2" s="37"/>
+      <c r="M2" s="36"/>
     </row>
     <row r="3" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
@@ -901,16 +871,16 @@
       </c>
       <c r="E3" s="17">
         <f t="shared" si="1"/>
-        <v>0.3507906319073727</v>
-      </c>
-      <c r="G3" s="45" t="s">
+        <v>0.35181447909034008</v>
+      </c>
+      <c r="G3" s="43" t="s">
         <v>43</v>
       </c>
-      <c r="H3" s="39">
+      <c r="H3" s="38">
         <f>8000+5000+8000+45000+136000+8000</f>
         <v>210000</v>
       </c>
-      <c r="I3" s="39">
+      <c r="I3" s="38">
         <v>0</v>
       </c>
     </row>
@@ -918,10 +888,10 @@
       <c r="A4" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B4" s="34">
+      <c r="B4" s="33">
         <v>3.1</v>
       </c>
-      <c r="C4" s="34">
+      <c r="C4" s="33">
         <v>431.11099999999999</v>
       </c>
       <c r="D4" s="19">
@@ -930,50 +900,50 @@
       </c>
       <c r="E4" s="17">
         <f t="shared" si="1"/>
-        <v>2.5970975412787513E-2</v>
-      </c>
-      <c r="G4" s="33"/>
-      <c r="H4" s="33"/>
+        <v>2.6046776496387484E-2</v>
+      </c>
+      <c r="G4" s="32"/>
+      <c r="H4" s="32"/>
       <c r="I4"/>
-      <c r="J4" s="33"/>
-      <c r="K4" s="33"/>
+      <c r="J4" s="32"/>
+      <c r="K4" s="32"/>
     </row>
     <row r="5" spans="1:121" x14ac:dyDescent="0.25">
-      <c r="A5" s="49" t="s">
-        <v>45</v>
-      </c>
-      <c r="B5">
+      <c r="A5" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="33">
         <v>6</v>
       </c>
-      <c r="C5">
-        <v>100.446</v>
+      <c r="C5" s="33">
+        <v>100.432</v>
       </c>
       <c r="D5" s="19">
         <f t="shared" si="0"/>
-        <v>602.67599999999993</v>
+        <v>602.59199999999998</v>
       </c>
       <c r="E5" s="17">
         <f t="shared" si="1"/>
-        <v>1.1711738319528011E-2</v>
+        <v>1.1744284061346918E-2</v>
       </c>
     </row>
     <row r="6" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B6" s="5">
-        <v>24.005400000000002</v>
+        <v>19.9191</v>
       </c>
       <c r="C6" s="18">
-        <v>100.63</v>
+        <v>121.23</v>
       </c>
       <c r="D6" s="19">
         <f t="shared" si="0"/>
-        <v>2415.6634020000001</v>
+        <v>2414.7924929999999</v>
       </c>
       <c r="E6" s="17">
         <f t="shared" si="1"/>
-        <v>4.6943328807327329E-2</v>
+        <v>4.7063367895690766E-2</v>
       </c>
     </row>
     <row r="7" spans="1:121" x14ac:dyDescent="0.25">
@@ -986,19 +956,19 @@
       <c r="C7" s="18">
         <v>638.44000000000005</v>
       </c>
-      <c r="D7" s="40">
+      <c r="D7" s="39">
         <f t="shared" si="0"/>
         <v>3183.9641240000001</v>
       </c>
       <c r="E7" s="17">
         <f t="shared" si="1"/>
-        <v>6.1873634654529538E-2</v>
-      </c>
-      <c r="G7" s="33"/>
-      <c r="H7" s="33"/>
+        <v>6.2054224273461321E-2</v>
+      </c>
+      <c r="G7" s="32"/>
+      <c r="H7" s="32"/>
       <c r="I7"/>
-      <c r="J7" s="33"/>
-      <c r="K7" s="33"/>
+      <c r="J7" s="32"/>
+      <c r="K7" s="32"/>
     </row>
     <row r="8" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
@@ -1008,21 +978,21 @@
         <v>6</v>
       </c>
       <c r="C8" s="14">
-        <v>301.79500000000002</v>
+        <v>301.053</v>
       </c>
       <c r="D8" s="15">
         <f t="shared" ref="D8:D9" si="2">C8*B8</f>
-        <v>1810.77</v>
+        <v>1806.318</v>
       </c>
       <c r="E8" s="17">
         <f t="shared" si="1"/>
-        <v>3.5188499951635276E-2</v>
-      </c>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
+        <v>3.5204436330260019E-2</v>
+      </c>
+      <c r="G8" s="32"/>
+      <c r="H8" s="32"/>
       <c r="I8"/>
-      <c r="J8" s="33"/>
-      <c r="K8" s="33"/>
+      <c r="J8" s="32"/>
+      <c r="K8" s="32"/>
     </row>
     <row r="9" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
@@ -1034,15 +1004,15 @@
       <c r="C9" s="18">
         <v>71.781999999999996</v>
       </c>
-      <c r="D9" s="39">
+      <c r="D9" s="38">
         <f t="shared" si="2"/>
         <v>1076.73</v>
       </c>
       <c r="E9" s="17">
         <f t="shared" si="1"/>
-        <v>2.0923979054724921E-2</v>
-      </c>
-      <c r="M9" s="37"/>
+        <v>2.0985049548241711E-2</v>
+      </c>
+      <c r="M9" s="36"/>
     </row>
     <row r="10" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
@@ -1054,21 +1024,21 @@
       <c r="C10" s="18">
         <v>15.927</v>
       </c>
-      <c r="D10" s="40">
+      <c r="D10" s="39">
         <f>B10*C10</f>
         <v>2946.4949999999999</v>
       </c>
       <c r="E10" s="17">
         <f t="shared" si="1"/>
-        <v>5.7258922538474553E-2</v>
-      </c>
-      <c r="G10" s="33"/>
-      <c r="H10" s="33"/>
+        <v>5.7426043268643444E-2</v>
+      </c>
+      <c r="G10" s="32"/>
+      <c r="H10" s="32"/>
       <c r="I10"/>
-      <c r="J10" s="33"/>
-      <c r="K10" s="33"/>
-    </row>
-    <row r="11" spans="1:121" s="34" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J10" s="32"/>
+      <c r="K10" s="32"/>
+    </row>
+    <row r="11" spans="1:121" s="33" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>18</v>
       </c>
@@ -1084,14 +1054,14 @@
       </c>
       <c r="E11" s="17">
         <f t="shared" si="1"/>
-        <v>0.13973004180002918</v>
+        <v>0.14013786970836012</v>
       </c>
       <c r="F11"/>
-      <c r="G11" s="33"/>
-      <c r="H11" s="33"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="32"/>
       <c r="I11"/>
-      <c r="J11" s="33"/>
-      <c r="K11" s="33"/>
+      <c r="J11" s="32"/>
+      <c r="K11" s="32"/>
       <c r="L11"/>
       <c r="M11"/>
       <c r="N11"/>
@@ -1208,22 +1178,22 @@
         <v>36</v>
       </c>
       <c r="B12" s="5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" s="18">
-        <v>91.68</v>
+        <v>86.221000000000004</v>
       </c>
       <c r="D12" s="19">
         <f t="shared" si="3"/>
-        <v>916.80000000000007</v>
+        <v>948.43100000000004</v>
       </c>
       <c r="E12" s="17">
         <f t="shared" si="1"/>
-        <v>1.7816076451266157E-2</v>
-      </c>
-      <c r="J12" s="33"/>
-      <c r="K12" s="33"/>
-      <c r="L12" s="33"/>
+        <v>1.8484551863594805E-2</v>
+      </c>
+      <c r="J12" s="32"/>
+      <c r="K12" s="32"/>
+      <c r="L12" s="32"/>
     </row>
     <row r="13" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
@@ -1233,19 +1203,19 @@
         <v>5.6</v>
       </c>
       <c r="C13" s="18">
-        <v>196.43199999999999</v>
+        <v>186.43199999999999</v>
       </c>
       <c r="D13" s="19">
         <f t="shared" si="3"/>
-        <v>1100.0192</v>
+        <v>1044.0192</v>
       </c>
       <c r="E13" s="17">
         <f t="shared" si="1"/>
-        <v>2.1376555590162126E-2</v>
-      </c>
-      <c r="J13" s="33"/>
-      <c r="K13" s="33"/>
-      <c r="L13" s="33"/>
+        <v>2.0347528759592164E-2</v>
+      </c>
+      <c r="J13" s="32"/>
+      <c r="K13" s="32"/>
+      <c r="L13" s="32"/>
     </row>
     <row r="14" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
@@ -1265,9 +1235,9 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J14" s="33"/>
-      <c r="K14" s="33"/>
-      <c r="L14" s="33"/>
+      <c r="J14" s="32"/>
+      <c r="K14" s="32"/>
+      <c r="L14" s="32"/>
     </row>
     <row r="15" spans="1:121" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
@@ -1277,22 +1247,22 @@
         <v>1</v>
       </c>
       <c r="C15" s="18">
-        <v>210.02</v>
+        <v>209.99</v>
       </c>
       <c r="D15" s="19">
         <f t="shared" si="3"/>
-        <v>210.02</v>
+        <v>209.99</v>
       </c>
       <c r="E15" s="17">
         <f t="shared" si="1"/>
-        <v>4.0812962219621707E-3</v>
-      </c>
-      <c r="G15" s="33"/>
-      <c r="H15" s="33"/>
+        <v>4.0926235496691618E-3</v>
+      </c>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
       <c r="I15"/>
-      <c r="J15" s="33"/>
-      <c r="K15" s="33"/>
-      <c r="M15" s="37"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="32"/>
+      <c r="M15" s="36"/>
     </row>
     <row r="16" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
@@ -1310,11 +1280,11 @@
       </c>
       <c r="E16" s="17">
         <f t="shared" si="1"/>
-        <v>1.2530329511099931E-2</v>
-      </c>
-      <c r="J16" s="33"/>
-      <c r="K16" s="33"/>
-      <c r="L16" s="33"/>
+        <v>1.2566901589726535E-2</v>
+      </c>
+      <c r="J16" s="32"/>
+      <c r="K16" s="32"/>
+      <c r="L16" s="32"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
@@ -1330,14 +1300,14 @@
         <f t="shared" si="3"/>
         <v>1994.8389999999999</v>
       </c>
-      <c r="E17" s="52">
+      <c r="E17" s="49">
         <f t="shared" si="1"/>
-        <v>3.8765493163140631E-2</v>
+        <v>3.8878637407488356E-2</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B18" s="5">
         <v>1</v>
@@ -1349,14 +1319,14 @@
         <f t="shared" si="3"/>
         <v>249.38</v>
       </c>
-      <c r="E18" s="52">
+      <c r="E18" s="49">
         <f t="shared" si="1"/>
-        <v>4.846174896833283E-3</v>
+        <v>4.8603193524286662E-3</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B19" s="5">
         <v>1</v>
@@ -1368,35 +1338,35 @@
         <f>C19*B19</f>
         <v>48.87</v>
       </c>
-      <c r="E19" s="52">
+      <c r="E19" s="49">
         <f t="shared" si="1"/>
-        <v>9.4968548884530649E-4</v>
+        <v>9.5245732116925534E-4</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D20" s="20">
         <f>SUM(D2:D19)</f>
-        <v>48480.497219480007</v>
+        <v>48450.691310480004</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="J21" s="33"/>
-      <c r="K21" s="33"/>
-      <c r="L21" s="33"/>
+      <c r="J21" s="32"/>
+      <c r="K21" s="32"/>
+      <c r="L21" s="32"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="41" t="s">
+      <c r="A22" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="B22" s="42"/>
-      <c r="C22" s="42"/>
-      <c r="E22" s="34"/>
-      <c r="J22" s="33"/>
-      <c r="K22" s="33"/>
-      <c r="L22" s="33"/>
+      <c r="B22" s="50"/>
+      <c r="C22" s="50"/>
+      <c r="E22"/>
+      <c r="J22" s="32"/>
+      <c r="K22" s="32"/>
+      <c r="L22" s="32"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="23" t="s">
+      <c r="A23" s="22" t="s">
         <v>6</v>
       </c>
       <c r="B23" s="22" t="s">
@@ -1405,38 +1375,38 @@
       <c r="C23" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D23" s="23" t="s">
+      <c r="D23" s="22" t="s">
         <v>16</v>
       </c>
       <c r="E23" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="J23" s="33"/>
-      <c r="K23" s="33"/>
-      <c r="L23" s="33"/>
+      <c r="J23" s="32"/>
+      <c r="K23" s="32"/>
+      <c r="L23" s="32"/>
     </row>
     <row r="24" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="34" t="s">
+      <c r="A24" s="33" t="s">
         <v>24</v>
       </c>
       <c r="B24" s="11">
         <v>1.278341E-2</v>
       </c>
-      <c r="C24" s="24">
+      <c r="C24" s="23">
         <v>76477.34</v>
       </c>
-      <c r="D24" s="24">
+      <c r="D24" s="23">
         <f>C24*B24</f>
         <v>977.64119292939995</v>
       </c>
       <c r="E24" s="16">
         <f>D24/(D20+D24+D25+B28+B72)</f>
-        <v>1.9044257789878966E-2</v>
-      </c>
-      <c r="H24" s="47"/>
-      <c r="J24" s="33"/>
-      <c r="K24" s="33"/>
-      <c r="L24" s="33"/>
+        <v>1.9055321561754664E-2</v>
+      </c>
+      <c r="H24" s="45"/>
+      <c r="J24" s="32"/>
+      <c r="K24" s="32"/>
+      <c r="L24" s="32"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
@@ -1448,33 +1418,33 @@
       <c r="C25" s="15">
         <v>69132.929999999993</v>
       </c>
-      <c r="D25" s="24">
+      <c r="D25" s="23">
         <f>C25*B25</f>
         <v>376.08313920000001</v>
       </c>
       <c r="E25" s="16">
         <f>D25/(D20+D24+D25+B28+B29)</f>
-        <v>7.308383464244516E-3</v>
-      </c>
-      <c r="J25" s="33"/>
-      <c r="K25" s="33"/>
-      <c r="L25" s="33"/>
+        <v>7.3297143298415423E-3</v>
+      </c>
+      <c r="J25" s="32"/>
+      <c r="K25" s="32"/>
+      <c r="L25" s="32"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="J26" s="33"/>
-      <c r="K26" s="33"/>
+      <c r="J26" s="32"/>
+      <c r="K26" s="32"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B27" s="23" t="s">
+      <c r="B27" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="C27" s="36" t="s">
+      <c r="C27" s="35" t="s">
         <v>15</v>
       </c>
       <c r="D27" s="9"/>
       <c r="E27" s="12"/>
-      <c r="J27" s="33"/>
-      <c r="K27" s="33"/>
+      <c r="J27" s="32"/>
+      <c r="K27" s="32"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
@@ -1483,55 +1453,55 @@
       <c r="B28" s="7">
         <v>1501</v>
       </c>
-      <c r="C28" s="43">
+      <c r="C28" s="41">
         <f>B28/(D20+B29)</f>
-        <v>3.088196682252203E-2</v>
-      </c>
-      <c r="D28" s="26"/>
+        <v>3.0977411860999976E-2</v>
+      </c>
+      <c r="D28" s="25"/>
       <c r="E28" s="12"/>
-      <c r="I28" s="33"/>
-      <c r="J28" s="33"/>
-      <c r="K28" s="33"/>
+      <c r="I28" s="32"/>
+      <c r="J28" s="32"/>
+      <c r="K28" s="32"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
         <v>39</v>
       </c>
       <c r="B29" s="7">
-        <v>123.92</v>
-      </c>
-      <c r="C29" s="43">
+        <v>3.97</v>
+      </c>
+      <c r="C29" s="41">
         <f>B29/D20</f>
-        <v>2.5560793949573513E-3</v>
-      </c>
-      <c r="D29" s="26"/>
+        <v>8.1938975329775725E-5</v>
+      </c>
+      <c r="D29" s="25"/>
       <c r="E29" s="12"/>
-      <c r="I29" s="33"/>
-      <c r="J29" s="33"/>
-      <c r="K29" s="33"/>
+      <c r="I29" s="32"/>
+      <c r="J29" s="32"/>
+      <c r="K29" s="32"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="J30" s="33"/>
-      <c r="K30" s="33"/>
-    </row>
-    <row r="31" spans="1:12" s="33" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J30" s="32"/>
+      <c r="K30" s="32"/>
+    </row>
+    <row r="31" spans="1:12" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31"/>
-      <c r="B31" s="27">
+      <c r="B31" s="26">
         <v>46057</v>
       </c>
-      <c r="C31" s="27">
+      <c r="C31" s="26">
         <v>46086</v>
       </c>
-      <c r="D31" s="27">
+      <c r="D31" s="26">
         <v>46120</v>
       </c>
-      <c r="E31" s="27">
+      <c r="E31" s="26">
         <v>46147</v>
       </c>
-      <c r="F31" s="27">
+      <c r="F31" s="26">
         <v>46184</v>
       </c>
-      <c r="G31" s="27">
+      <c r="G31" s="26">
         <v>46210</v>
       </c>
       <c r="H31"/>
@@ -1543,7 +1513,7 @@
       <c r="A32" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B32" s="28">
+      <c r="B32" s="27">
         <v>21890.13</v>
       </c>
       <c r="C32" s="15">
@@ -1562,16 +1532,16 @@
         <v>21287.19</v>
       </c>
       <c r="I32" s="15">
-        <v>21166.38</v>
-      </c>
-      <c r="J32" s="33"/>
-      <c r="K32" s="33"/>
+        <v>19890.89</v>
+      </c>
+      <c r="J32" s="32"/>
+      <c r="K32" s="32"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="50" t="s">
+      <c r="A33" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="B33" s="28">
+      <c r="B33" s="27">
         <v>141.21</v>
       </c>
       <c r="C33" s="15">
@@ -1589,16 +1559,16 @@
       <c r="G33" s="15">
         <v>30268.1</v>
       </c>
-      <c r="H33" s="33"/>
+      <c r="H33" s="32"/>
       <c r="I33" s="15">
-        <v>30330.35</v>
+        <v>29906.49</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="29" t="s">
+      <c r="A34" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="B34" s="28">
+      <c r="B34" s="27">
         <v>537.24</v>
       </c>
       <c r="C34" s="15">
@@ -1617,32 +1587,32 @@
         <v>1164.81</v>
       </c>
       <c r="I34" s="15">
-        <f>63119.84*B25+63119.84*B24</f>
-        <v>1150.2587234544001</v>
+        <f>65483.24*B25+ 65483.24*B24</f>
+        <v>1193.3279306484001</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="9"/>
       <c r="B35" s="9"/>
-      <c r="C35" s="25"/>
+      <c r="C35" s="24"/>
       <c r="D35" s="21"/>
       <c r="E35" s="12"/>
       <c r="F35" s="9"/>
       <c r="G35" s="9"/>
-      <c r="I35" s="25"/>
+      <c r="I35" s="24"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B36" s="28">
+      <c r="B36" s="27">
         <v>22603.38</v>
       </c>
-      <c r="C36" s="35">
+      <c r="C36" s="34">
         <f>SUM(C32:C34)</f>
         <v>26802.61</v>
       </c>
-      <c r="D36" s="35">
+      <c r="D36" s="34">
         <f>SUM(D32:D34)</f>
         <v>29026.09</v>
       </c>
@@ -1655,16 +1625,16 @@
       <c r="G36" s="15">
         <v>52720.1</v>
       </c>
-      <c r="I36" s="35">
+      <c r="I36" s="34">
         <f>SUM(I32:I34)</f>
-        <v>52646.988723454393</v>
+        <v>50990.707930648408</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B37" s="28">
+      <c r="B37" s="27">
         <v>20582.53</v>
       </c>
       <c r="C37" s="15">
@@ -1685,7 +1655,7 @@
       <c r="H37" s="9"/>
       <c r="I37" s="15">
         <f>D20+D24+D25+B28+B29</f>
-        <v>51459.141551609398</v>
+        <v>51309.385642609399</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -1696,13 +1666,13 @@
       <c r="E38" s="12"/>
       <c r="F38" s="9"/>
       <c r="G38" s="9"/>
-      <c r="J38" s="37"/>
+      <c r="J38" s="36"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B39" s="30">
+      <c r="B39" s="29">
         <f t="shared" ref="B39:G39" si="4">B36-B37</f>
         <v>2020.8500000000022</v>
       </c>
@@ -1728,14 +1698,14 @@
       </c>
       <c r="I39" s="15">
         <f>I36-I37</f>
-        <v>1187.8471718449946</v>
+        <v>-318.67771196099056</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B40" s="28">
+      <c r="B40" s="27">
         <f>B39*7.783</f>
         <v>15728.275550000018</v>
       </c>
@@ -1761,7 +1731,7 @@
       </c>
       <c r="I40" s="15">
         <f>I39*7.8</f>
-        <v>9265.2079403909574</v>
+        <v>-2485.6861532957264</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -1777,7 +1747,7 @@
       <c r="A42" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B42" s="31">
+      <c r="B42" s="30">
         <v>0.1012</v>
       </c>
       <c r="C42" s="16">
@@ -1789,77 +1759,77 @@
       <c r="E42" s="16">
         <v>0.16200000000000001</v>
       </c>
-      <c r="F42" s="32">
+      <c r="F42" s="31">
         <f>(F39/F37)</f>
         <v>8.0251934420664094E-3</v>
       </c>
-      <c r="G42" s="32">
+      <c r="G42" s="31">
         <f>(G39/G37)</f>
         <v>2.5938765271805112E-2</v>
       </c>
       <c r="I42" s="16">
         <f>(I39/I37)</f>
-        <v>2.3083307183694057E-2</v>
+        <v>-6.2109048465461966E-3</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B44" s="34"/>
-      <c r="C44" s="38">
+      <c r="B44" s="33"/>
+      <c r="C44" s="37">
         <f>(C36-B36)/B37</f>
         <v>0.20401913661731574</v>
       </c>
-      <c r="D44" s="38">
+      <c r="D44" s="37">
         <f>(D36-C36)/C37</f>
         <v>9.4447450894104903E-2</v>
       </c>
-      <c r="E44" s="38">
+      <c r="E44" s="37">
         <f>(E36-D36)/D37</f>
         <v>9.7117918270353529E-2</v>
       </c>
-      <c r="F44" s="38">
+      <c r="F44" s="37">
         <f>(F36-E36)/E37</f>
         <v>-0.11428987916805573</v>
       </c>
-      <c r="G44" s="38">
+      <c r="G44" s="37">
         <f>(G36-F36)/F37</f>
         <v>0.85637792992234019</v>
       </c>
-      <c r="I44" s="51"/>
+      <c r="I44" s="48"/>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A46" s="44" t="s">
+      <c r="A46" s="42" t="s">
         <v>29</v>
       </c>
-      <c r="B46" s="34">
+      <c r="B46" s="33">
         <v>0</v>
       </c>
-      <c r="C46" s="38">
+      <c r="C46" s="37">
         <f>(C36-$B$36)/$B$36</f>
         <v>0.18577885254329218</v>
       </c>
-      <c r="D46" s="38">
+      <c r="D46" s="37">
         <f>(D36-$B$36)/$B$36</f>
         <v>0.2841482114621795</v>
       </c>
-      <c r="E46" s="38">
+      <c r="E46" s="37">
         <f>(E36-$B$36)/$B$36</f>
         <v>0.39876248596448838</v>
       </c>
-      <c r="F46" s="38">
+      <c r="F46" s="37">
         <f>(F36-$B$36)/$B$36</f>
         <v>0.26105608984143081</v>
       </c>
-      <c r="G46" s="38">
+      <c r="G46" s="37">
         <f>(G36-$B$36)/$B$36</f>
         <v>1.3323989598015871</v>
       </c>
-      <c r="H46" s="51"/>
-      <c r="I46" s="38">
+      <c r="H46" s="48"/>
+      <c r="I46" s="37">
         <f>(I36-$B$36)/$B$36</f>
-        <v>1.3291644313131217</v>
+        <v>1.2558886295168425</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
@@ -1869,15 +1839,15 @@
       <c r="F53" s="9"/>
       <c r="G53" s="9"/>
       <c r="H53" s="9"/>
-      <c r="I53" s="33"/>
+      <c r="I53" s="32"/>
       <c r="J53" s="9"/>
       <c r="K53" s="9"/>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="I54" s="33"/>
+      <c r="I54" s="32"/>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="I55" s="33"/>
+      <c r="I55" s="32"/>
     </row>
   </sheetData>
   <autoFilter ref="E1:E16" xr:uid="{280FFEA0-C244-4411-A4EA-E725FEE5A5C2}">

--- a/Portfolio.xlsx
+++ b/Portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\john.hcpang\Documents\Practice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72B8CCB8-4538-4E32-87D3-DA702EBB90EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABE523A6-0A7E-41D1-89ED-D168F05CD3A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{E7CDDCE8-D664-4969-9A02-FA9A05E60C5E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="47">
   <si>
     <t>Shares</t>
   </si>
@@ -171,9 +171,6 @@
   </si>
   <si>
     <t>Ibkr</t>
-  </si>
-  <si>
-    <t>SGOV(in webull)</t>
   </si>
   <si>
     <t>VSH</t>
@@ -828,21 +825,21 @@
     </row>
     <row r="2" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="B2" s="5">
-        <v>6.4302000000000001</v>
-      </c>
-      <c r="C2" s="14">
-        <v>731.12090000000001</v>
-      </c>
-      <c r="D2" s="15">
-        <f t="shared" ref="D2:D7" si="0">C2*B2</f>
-        <v>4701.25361118</v>
+        <v>974.01310000000001</v>
+      </c>
+      <c r="C2" s="18">
+        <v>18.533000000000001</v>
+      </c>
+      <c r="D2" s="19">
+        <f>C2*B2</f>
+        <v>18051.3847823</v>
       </c>
       <c r="E2" s="17">
-        <f t="shared" ref="E2:E19" si="1">D2/($D$20+$D$24+$D$25+$B$29+$B$28)</f>
-        <v>9.1625607134065701E-2</v>
+        <f>D2/($D$19+$D$24+$D$25+$B$29+$B$28)</f>
+        <v>0.35381903861691627</v>
       </c>
       <c r="G2" s="43" t="s">
         <v>40</v>
@@ -857,21 +854,21 @@
     </row>
     <row r="3" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="B3" s="5">
-        <v>974.01310000000001</v>
-      </c>
-      <c r="C3" s="18">
-        <v>18.533000000000001</v>
-      </c>
-      <c r="D3" s="19">
-        <f t="shared" si="0"/>
-        <v>18051.3847823</v>
+        <v>18</v>
+      </c>
+      <c r="C3" s="14">
+        <v>399.46600000000001</v>
+      </c>
+      <c r="D3" s="15">
+        <f>C3*B3</f>
+        <v>7190.3879999999999</v>
       </c>
       <c r="E3" s="17">
-        <f t="shared" si="1"/>
-        <v>0.35181447909034008</v>
+        <f>D3/($D$19+$D$24+$D$25+$B$29+$B$28)</f>
+        <v>0.14093634367249125</v>
       </c>
       <c r="G3" s="43" t="s">
         <v>43</v>
@@ -886,21 +883,21 @@
     </row>
     <row r="4" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B4" s="33">
-        <v>3.1</v>
-      </c>
-      <c r="C4" s="33">
-        <v>431.11099999999999</v>
-      </c>
-      <c r="D4" s="19">
-        <f t="shared" si="0"/>
-        <v>1336.4440999999999</v>
+        <v>22</v>
+      </c>
+      <c r="B4" s="5">
+        <v>6.4302000000000001</v>
+      </c>
+      <c r="C4" s="14">
+        <v>731.12090000000001</v>
+      </c>
+      <c r="D4" s="15">
+        <f>C4*B4</f>
+        <v>4701.25361118</v>
       </c>
       <c r="E4" s="17">
-        <f t="shared" si="1"/>
-        <v>2.6046776496387484E-2</v>
+        <f>D4/($D$19+$D$24+$D$25+$B$29+$B$28)</f>
+        <v>9.2147669171233182E-2</v>
       </c>
       <c r="G4" s="32"/>
       <c r="H4" s="32"/>
@@ -910,59 +907,59 @@
     </row>
     <row r="5" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B5" s="33">
-        <v>6</v>
-      </c>
-      <c r="C5" s="33">
-        <v>100.432</v>
-      </c>
-      <c r="D5" s="19">
-        <f t="shared" si="0"/>
-        <v>602.59199999999998</v>
+        <v>34</v>
+      </c>
+      <c r="B5" s="5">
+        <v>4.9870999999999999</v>
+      </c>
+      <c r="C5" s="18">
+        <v>638.44000000000005</v>
+      </c>
+      <c r="D5" s="39">
+        <f>C5*B5</f>
+        <v>3183.9641240000001</v>
       </c>
       <c r="E5" s="17">
-        <f t="shared" si="1"/>
-        <v>1.1744284061346918E-2</v>
+        <f>D5/($D$19+$D$24+$D$25+$B$29+$B$28)</f>
+        <v>6.2407795242891834E-2</v>
       </c>
     </row>
     <row r="6" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="B6" s="5">
-        <v>19.9191</v>
+        <v>185</v>
       </c>
       <c r="C6" s="18">
-        <v>121.23</v>
-      </c>
-      <c r="D6" s="19">
-        <f t="shared" si="0"/>
-        <v>2414.7924929999999</v>
+        <v>15.927</v>
+      </c>
+      <c r="D6" s="39">
+        <f>B6*C6</f>
+        <v>2946.4949999999999</v>
       </c>
       <c r="E6" s="17">
-        <f t="shared" si="1"/>
-        <v>4.7063367895690766E-2</v>
+        <f>D6/($D$19+$D$24+$D$25+$B$29+$B$28)</f>
+        <v>5.77532439069042E-2</v>
       </c>
     </row>
     <row r="7" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="B7" s="5">
-        <v>4.9870999999999999</v>
+        <v>19.9191</v>
       </c>
       <c r="C7" s="18">
-        <v>638.44000000000005</v>
-      </c>
-      <c r="D7" s="39">
-        <f t="shared" si="0"/>
-        <v>3183.9641240000001</v>
+        <v>121.23</v>
+      </c>
+      <c r="D7" s="19">
+        <f>C7*B7</f>
+        <v>2414.7924929999999</v>
       </c>
       <c r="E7" s="17">
-        <f t="shared" si="1"/>
-        <v>6.2054224273461321E-2</v>
+        <f>D7/($D$19+$D$24+$D$25+$B$29+$B$28)</f>
+        <v>4.7331524347670795E-2</v>
       </c>
       <c r="G7" s="32"/>
       <c r="H7" s="32"/>
@@ -972,21 +969,21 @@
     </row>
     <row r="8" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B8" s="5">
-        <v>6</v>
-      </c>
-      <c r="C8" s="14">
-        <v>301.053</v>
-      </c>
-      <c r="D8" s="15">
-        <f t="shared" ref="D8:D9" si="2">C8*B8</f>
-        <v>1806.318</v>
-      </c>
-      <c r="E8" s="17">
-        <f t="shared" si="1"/>
-        <v>3.5204436330260019E-2</v>
+        <v>7</v>
+      </c>
+      <c r="C8" s="18">
+        <v>284.97699999999998</v>
+      </c>
+      <c r="D8" s="19">
+        <f>C8*B8</f>
+        <v>1994.8389999999999</v>
+      </c>
+      <c r="E8" s="49">
+        <f>D8/($D$19+$D$24+$D$25+$B$29+$B$28)</f>
+        <v>3.9100159111759861E-2</v>
       </c>
       <c r="G8" s="32"/>
       <c r="H8" s="32"/>
@@ -996,41 +993,41 @@
     </row>
     <row r="9" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B9" s="5">
-        <v>15</v>
-      </c>
-      <c r="C9" s="18">
-        <v>71.781999999999996</v>
-      </c>
-      <c r="D9" s="38">
-        <f t="shared" si="2"/>
-        <v>1076.73</v>
+        <v>6</v>
+      </c>
+      <c r="C9" s="14">
+        <v>301.053</v>
+      </c>
+      <c r="D9" s="15">
+        <f>C9*B9</f>
+        <v>1806.318</v>
       </c>
       <c r="E9" s="17">
-        <f t="shared" si="1"/>
-        <v>2.0985049548241711E-2</v>
+        <f>D9/($D$19+$D$24+$D$25+$B$29+$B$28)</f>
+        <v>3.5405023265755203E-2</v>
       </c>
       <c r="M9" s="36"/>
     </row>
     <row r="10" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" s="5">
-        <v>185</v>
-      </c>
-      <c r="C10" s="18">
-        <v>15.927</v>
-      </c>
-      <c r="D10" s="39">
-        <f>B10*C10</f>
-        <v>2946.4949999999999</v>
+        <v>33</v>
+      </c>
+      <c r="B10" s="33">
+        <v>3.1</v>
+      </c>
+      <c r="C10" s="33">
+        <v>431.11099999999999</v>
+      </c>
+      <c r="D10" s="19">
+        <f>C10*B10</f>
+        <v>1336.4440999999999</v>
       </c>
       <c r="E10" s="17">
-        <f t="shared" si="1"/>
-        <v>5.7426043268643444E-2</v>
+        <f>D10/($D$19+$D$24+$D$25+$B$29+$B$28)</f>
+        <v>2.6195185152271788E-2</v>
       </c>
       <c r="G10" s="32"/>
       <c r="H10" s="32"/>
@@ -1040,21 +1037,21 @@
     </row>
     <row r="11" spans="1:121" s="33" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B11" s="5">
-        <v>18</v>
-      </c>
-      <c r="C11" s="14">
-        <v>399.46600000000001</v>
-      </c>
-      <c r="D11" s="15">
-        <f t="shared" ref="D11:D18" si="3">C11*B11</f>
-        <v>7190.3879999999999</v>
+        <v>15</v>
+      </c>
+      <c r="C11" s="18">
+        <v>71.781999999999996</v>
+      </c>
+      <c r="D11" s="38">
+        <f>C11*B11</f>
+        <v>1076.73</v>
       </c>
       <c r="E11" s="17">
-        <f t="shared" si="1"/>
-        <v>0.14013786970836012</v>
+        <f>D11/($D$19+$D$24+$D$25+$B$29+$B$28)</f>
+        <v>2.1104617625986456E-2</v>
       </c>
       <c r="F11"/>
       <c r="G11" s="32"/>
@@ -1175,21 +1172,21 @@
     </row>
     <row r="12" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="B12" s="5">
-        <v>11</v>
+        <v>5.6</v>
       </c>
       <c r="C12" s="18">
-        <v>86.221000000000004</v>
+        <v>186.43199999999999</v>
       </c>
       <c r="D12" s="19">
-        <f t="shared" si="3"/>
-        <v>948.43100000000004</v>
+        <f>C12*B12</f>
+        <v>1044.0192</v>
       </c>
       <c r="E12" s="17">
-        <f t="shared" si="1"/>
-        <v>1.8484551863594805E-2</v>
+        <f>D12/($D$19+$D$24+$D$25+$B$29+$B$28)</f>
+        <v>2.0463464387718629E-2</v>
       </c>
       <c r="J12" s="32"/>
       <c r="K12" s="32"/>
@@ -1197,21 +1194,21 @@
     </row>
     <row r="13" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="B13" s="5">
-        <v>5.6</v>
+        <v>11</v>
       </c>
       <c r="C13" s="18">
-        <v>186.43199999999999</v>
+        <v>86.221000000000004</v>
       </c>
       <c r="D13" s="19">
-        <f t="shared" si="3"/>
-        <v>1044.0192</v>
+        <f>C13*B13</f>
+        <v>948.43100000000004</v>
       </c>
       <c r="E13" s="17">
-        <f t="shared" si="1"/>
-        <v>2.0347528759592164E-2</v>
+        <f>D13/($D$19+$D$24+$D$25+$B$29+$B$28)</f>
+        <v>1.8589872669686886E-2</v>
       </c>
       <c r="J13" s="32"/>
       <c r="K13" s="32"/>
@@ -1219,21 +1216,21 @@
     </row>
     <row r="14" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="B14" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C14" s="18">
-        <v>0</v>
+        <v>255.13300000000001</v>
       </c>
       <c r="D14" s="19">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="E14" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>C14*B14</f>
+        <v>765.399</v>
+      </c>
+      <c r="E14" s="49">
+        <f>D14/($D$19+$D$24+$D$25+$B$29+$B$28)</f>
+        <v>1.5002324841243773E-2</v>
       </c>
       <c r="J14" s="32"/>
       <c r="K14" s="32"/>
@@ -1241,21 +1238,21 @@
     </row>
     <row r="15" spans="1:121" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="B15" s="5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C15" s="18">
-        <v>209.99</v>
+        <v>80.599999999999994</v>
       </c>
       <c r="D15" s="19">
-        <f t="shared" si="3"/>
-        <v>209.99</v>
+        <f>C15*B15</f>
+        <v>644.79999999999995</v>
       </c>
       <c r="E15" s="17">
-        <f t="shared" si="1"/>
-        <v>4.0926235496691618E-3</v>
+        <f>D15/($D$19+$D$24+$D$25+$B$29+$B$28)</f>
+        <v>1.2638504959679832E-2</v>
       </c>
       <c r="G15" s="32"/>
       <c r="H15" s="32"/>
@@ -1266,21 +1263,21 @@
     </row>
     <row r="16" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="B16" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C16" s="18">
-        <v>80.599999999999994</v>
+        <v>209.99</v>
       </c>
       <c r="D16" s="19">
-        <f t="shared" si="3"/>
-        <v>644.79999999999995</v>
+        <f>C16*B16</f>
+        <v>209.99</v>
       </c>
       <c r="E16" s="17">
-        <f t="shared" si="1"/>
-        <v>1.2566901589726535E-2</v>
+        <f>D16/($D$19+$D$24+$D$25+$B$29+$B$28)</f>
+        <v>4.1159423952902736E-3</v>
       </c>
       <c r="J16" s="32"/>
       <c r="K16" s="32"/>
@@ -1288,65 +1285,45 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="B17" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C17" s="18">
-        <v>284.97699999999998</v>
+        <v>48.87</v>
       </c>
       <c r="D17" s="19">
-        <f t="shared" si="3"/>
-        <v>1994.8389999999999</v>
+        <f>C17*B17</f>
+        <v>48.87</v>
       </c>
       <c r="E17" s="49">
-        <f t="shared" si="1"/>
-        <v>3.8878637407488356E-2</v>
+        <f>D17/($D$19+$D$24+$D$25+$B$29+$B$28)</f>
+        <v>9.5788420809484094E-4</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="B18" s="5">
         <v>1</v>
       </c>
       <c r="C18" s="18">
-        <v>249.38</v>
+        <v>-291.61</v>
       </c>
       <c r="D18" s="19">
-        <f t="shared" si="3"/>
-        <v>249.38</v>
-      </c>
-      <c r="E18" s="49">
-        <f t="shared" si="1"/>
-        <v>4.8603193524286662E-3</v>
+        <f>C18*B18</f>
+        <v>-291.61</v>
+      </c>
+      <c r="E18" s="17">
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B19" s="5">
-        <v>1</v>
-      </c>
-      <c r="C19" s="18">
-        <v>48.87</v>
-      </c>
-      <c r="D19" s="19">
-        <f>C19*B19</f>
-        <v>48.87</v>
-      </c>
-      <c r="E19" s="49">
-        <f t="shared" si="1"/>
-        <v>9.5245732116925534E-4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D20" s="20">
-        <f>SUM(D2:D19)</f>
-        <v>48450.691310480004</v>
+      <c r="D19" s="20">
+        <f>SUM(D2:D18)</f>
+        <v>48072.508310480007</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
@@ -1400,8 +1377,8 @@
         <v>977.64119292939995</v>
       </c>
       <c r="E24" s="16">
-        <f>D24/(D20+D24+D25+B28+B72)</f>
-        <v>1.9055321561754664E-2</v>
+        <f>D24/(D19+D24+D25+B28+B72)</f>
+        <v>1.9196825395759568E-2</v>
       </c>
       <c r="H24" s="45"/>
       <c r="J24" s="32"/>
@@ -1423,8 +1400,8 @@
         <v>376.08313920000001</v>
       </c>
       <c r="E25" s="16">
-        <f>D25/(D20+D24+D25+B28+B29)</f>
-        <v>7.3297143298415423E-3</v>
+        <f>D25/(D19+D24+D25+B28+B29)</f>
+        <v>7.3714773883857962E-3</v>
       </c>
       <c r="J25" s="32"/>
       <c r="K25" s="32"/>
@@ -1454,8 +1431,8 @@
         <v>1501</v>
       </c>
       <c r="C28" s="41">
-        <f>B28/(D20+B29)</f>
-        <v>3.0977411860999976E-2</v>
+        <f>B28/(D19+B29)</f>
+        <v>3.1164375624618063E-2</v>
       </c>
       <c r="D28" s="25"/>
       <c r="E28" s="12"/>
@@ -1468,11 +1445,11 @@
         <v>39</v>
       </c>
       <c r="B29" s="7">
-        <v>3.97</v>
+        <v>91.46</v>
       </c>
       <c r="C29" s="41">
-        <f>B29/D20</f>
-        <v>8.1938975329775725E-5</v>
+        <f>B29/D19</f>
+        <v>1.9025427050591685E-3</v>
       </c>
       <c r="D29" s="25"/>
       <c r="E29" s="12"/>
@@ -1532,7 +1509,7 @@
         <v>21287.19</v>
       </c>
       <c r="I32" s="15">
-        <v>19890.89</v>
+        <v>20350.72</v>
       </c>
       <c r="J32" s="32"/>
       <c r="K32" s="32"/>
@@ -1561,7 +1538,7 @@
       </c>
       <c r="H33" s="32"/>
       <c r="I33" s="15">
-        <v>29906.49</v>
+        <v>30104.35</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -1587,8 +1564,8 @@
         <v>1164.81</v>
       </c>
       <c r="I34" s="15">
-        <f>65483.24*B25+ 65483.24*B24</f>
-        <v>1193.3279306484001</v>
+        <f>66388*B25+ 66388*B24</f>
+        <v>1209.8157430799999</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -1627,7 +1604,7 @@
       </c>
       <c r="I36" s="34">
         <f>SUM(I32:I34)</f>
-        <v>50990.707930648408</v>
+        <v>51664.885743079998</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -1654,8 +1631,8 @@
       </c>
       <c r="H37" s="9"/>
       <c r="I37" s="15">
-        <f>D20+D24+D25+B28+B29</f>
-        <v>51309.385642609399</v>
+        <f>D19+D24+D25+B28+B29</f>
+        <v>51018.692642609407</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -1673,32 +1650,32 @@
         <v>11</v>
       </c>
       <c r="B39" s="29">
-        <f t="shared" ref="B39:G39" si="4">B36-B37</f>
+        <f t="shared" ref="B39:G39" si="0">B36-B37</f>
         <v>2020.8500000000022</v>
       </c>
       <c r="C39" s="15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>3260.630000000001</v>
       </c>
       <c r="D39" s="15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>2350.5800000000017</v>
       </c>
       <c r="E39" s="15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>4382.239999999998</v>
       </c>
       <c r="F39" s="15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>226.93000000000029</v>
       </c>
       <c r="G39" s="15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>1332.9199999999983</v>
       </c>
       <c r="I39" s="15">
         <f>I36-I37</f>
-        <v>-318.67771196099056</v>
+        <v>646.19310047059116</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
@@ -1731,7 +1708,7 @@
       </c>
       <c r="I40" s="15">
         <f>I39*7.8</f>
-        <v>-2485.6861532957264</v>
+        <v>5040.3061836706111</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -1769,7 +1746,7 @@
       </c>
       <c r="I42" s="16">
         <f>(I39/I37)</f>
-        <v>-6.2109048465461966E-3</v>
+        <v>1.2665810647035446E-2</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
@@ -1829,7 +1806,7 @@
       <c r="H46" s="48"/>
       <c r="I46" s="37">
         <f>(I36-$B$36)/$B$36</f>
-        <v>1.2558886295168425</v>
+        <v>1.2857150454082529</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
@@ -1851,7 +1828,7 @@
     </row>
   </sheetData>
   <autoFilter ref="E1:E16" xr:uid="{280FFEA0-C244-4411-A4EA-E725FEE5A5C2}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E17">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E19">
       <sortCondition descending="1" ref="E1:E16"/>
     </sortState>
   </autoFilter>

--- a/Portfolio.xlsx
+++ b/Portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\john.hcpang\Documents\Practice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABE523A6-0A7E-41D1-89ED-D168F05CD3A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99EEA45F-497E-4881-9BC7-8E5AFC37BCD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{E7CDDCE8-D664-4969-9A02-FA9A05E60C5E}"/>
   </bookViews>
@@ -828,18 +828,18 @@
         <v>32</v>
       </c>
       <c r="B2" s="5">
-        <v>974.01310000000001</v>
+        <v>1055.8062</v>
       </c>
       <c r="C2" s="18">
         <v>18.533000000000001</v>
       </c>
       <c r="D2" s="19">
         <f>C2*B2</f>
-        <v>18051.3847823</v>
+        <v>19567.2563046</v>
       </c>
       <c r="E2" s="17">
-        <f>D2/($D$19+$D$24+$D$25+$B$29+$B$28)</f>
-        <v>0.35381903861691627</v>
+        <f t="shared" ref="E2:E17" si="0">D2/($D$19+$D$24+$D$25+$B$29+$B$28)</f>
+        <v>0.38340140053761917</v>
       </c>
       <c r="G2" s="43" t="s">
         <v>40</v>
@@ -867,8 +867,8 @@
         <v>7190.3879999999999</v>
       </c>
       <c r="E3" s="17">
-        <f>D3/($D$19+$D$24+$D$25+$B$29+$B$28)</f>
-        <v>0.14093634367249125</v>
+        <f t="shared" si="0"/>
+        <v>0.14088867579052472</v>
       </c>
       <c r="G3" s="43" t="s">
         <v>43</v>
@@ -896,8 +896,8 @@
         <v>4701.25361118</v>
       </c>
       <c r="E4" s="17">
-        <f>D4/($D$19+$D$24+$D$25+$B$29+$B$28)</f>
-        <v>9.2147669171233182E-2</v>
+        <f t="shared" si="0"/>
+        <v>9.2116502730391264E-2</v>
       </c>
       <c r="G4" s="32"/>
       <c r="H4" s="32"/>
@@ -920,8 +920,8 @@
         <v>3183.9641240000001</v>
       </c>
       <c r="E5" s="17">
-        <f>D5/($D$19+$D$24+$D$25+$B$29+$B$28)</f>
-        <v>6.2407795242891834E-2</v>
+        <f t="shared" si="0"/>
+        <v>6.2386687504888204E-2</v>
       </c>
     </row>
     <row r="6" spans="1:121" x14ac:dyDescent="0.25">
@@ -939,8 +939,8 @@
         <v>2946.4949999999999</v>
       </c>
       <c r="E6" s="17">
-        <f>D6/($D$19+$D$24+$D$25+$B$29+$B$28)</f>
-        <v>5.77532439069042E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.7733710444193294E-2</v>
       </c>
     </row>
     <row r="7" spans="1:121" x14ac:dyDescent="0.25">
@@ -954,12 +954,12 @@
         <v>121.23</v>
       </c>
       <c r="D7" s="19">
-        <f>C7*B7</f>
+        <f t="shared" ref="D7:D18" si="1">C7*B7</f>
         <v>2414.7924929999999</v>
       </c>
       <c r="E7" s="17">
-        <f>D7/($D$19+$D$24+$D$25+$B$29+$B$28)</f>
-        <v>4.7331524347670795E-2</v>
+        <f t="shared" si="0"/>
+        <v>4.7315515747922081E-2</v>
       </c>
       <c r="G7" s="32"/>
       <c r="H7" s="32"/>
@@ -978,12 +978,12 @@
         <v>284.97699999999998</v>
       </c>
       <c r="D8" s="19">
-        <f>C8*B8</f>
+        <f t="shared" si="1"/>
         <v>1994.8389999999999</v>
       </c>
       <c r="E8" s="49">
-        <f>D8/($D$19+$D$24+$D$25+$B$29+$B$28)</f>
-        <v>3.9100159111759861E-2</v>
+        <f t="shared" si="0"/>
+        <v>3.9086934547244816E-2</v>
       </c>
       <c r="G8" s="32"/>
       <c r="H8" s="32"/>
@@ -1002,12 +1002,12 @@
         <v>301.053</v>
       </c>
       <c r="D9" s="15">
-        <f>C9*B9</f>
+        <f t="shared" si="1"/>
         <v>1806.318</v>
       </c>
       <c r="E9" s="17">
-        <f>D9/($D$19+$D$24+$D$25+$B$29+$B$28)</f>
-        <v>3.5405023265755203E-2</v>
+        <f t="shared" si="0"/>
+        <v>3.5393048480358645E-2</v>
       </c>
       <c r="M9" s="36"/>
     </row>
@@ -1022,12 +1022,12 @@
         <v>431.11099999999999</v>
       </c>
       <c r="D10" s="19">
-        <f>C10*B10</f>
+        <f t="shared" si="1"/>
         <v>1336.4440999999999</v>
       </c>
       <c r="E10" s="17">
-        <f>D10/($D$19+$D$24+$D$25+$B$29+$B$28)</f>
-        <v>2.6195185152271788E-2</v>
+        <f t="shared" si="0"/>
+        <v>2.6186325343925752E-2</v>
       </c>
       <c r="G10" s="32"/>
       <c r="H10" s="32"/>
@@ -1046,12 +1046,12 @@
         <v>71.781999999999996</v>
       </c>
       <c r="D11" s="38">
-        <f>C11*B11</f>
+        <f t="shared" si="1"/>
         <v>1076.73</v>
       </c>
       <c r="E11" s="17">
-        <f>D11/($D$19+$D$24+$D$25+$B$29+$B$28)</f>
-        <v>2.1104617625986456E-2</v>
+        <f t="shared" si="0"/>
+        <v>2.1097479563541174E-2</v>
       </c>
       <c r="F11"/>
       <c r="G11" s="32"/>
@@ -1181,12 +1181,12 @@
         <v>186.43199999999999</v>
       </c>
       <c r="D12" s="19">
-        <f>C12*B12</f>
+        <f t="shared" si="1"/>
         <v>1044.0192</v>
       </c>
       <c r="E12" s="17">
-        <f>D12/($D$19+$D$24+$D$25+$B$29+$B$28)</f>
-        <v>2.0463464387718629E-2</v>
+        <f t="shared" si="0"/>
+        <v>2.0456543177904029E-2</v>
       </c>
       <c r="J12" s="32"/>
       <c r="K12" s="32"/>
@@ -1203,12 +1203,12 @@
         <v>86.221000000000004</v>
       </c>
       <c r="D13" s="19">
-        <f>C13*B13</f>
+        <f t="shared" si="1"/>
         <v>948.43100000000004</v>
       </c>
       <c r="E13" s="17">
-        <f>D13/($D$19+$D$24+$D$25+$B$29+$B$28)</f>
-        <v>1.8589872669686886E-2</v>
+        <f t="shared" si="0"/>
+        <v>1.8583585151271832E-2</v>
       </c>
       <c r="J13" s="32"/>
       <c r="K13" s="32"/>
@@ -1225,12 +1225,12 @@
         <v>255.13300000000001</v>
       </c>
       <c r="D14" s="19">
-        <f>C14*B14</f>
+        <f t="shared" si="1"/>
         <v>765.399</v>
       </c>
       <c r="E14" s="49">
-        <f>D14/($D$19+$D$24+$D$25+$B$29+$B$28)</f>
-        <v>1.5002324841243773E-2</v>
+        <f t="shared" si="0"/>
+        <v>1.4997250713228804E-2</v>
       </c>
       <c r="J14" s="32"/>
       <c r="K14" s="32"/>
@@ -1247,12 +1247,12 @@
         <v>80.599999999999994</v>
       </c>
       <c r="D15" s="19">
-        <f>C15*B15</f>
+        <f t="shared" si="1"/>
         <v>644.79999999999995</v>
       </c>
       <c r="E15" s="17">
-        <f>D15/($D$19+$D$24+$D$25+$B$29+$B$28)</f>
-        <v>1.2638504959679832E-2</v>
+        <f t="shared" si="0"/>
+        <v>1.2634230329396735E-2</v>
       </c>
       <c r="G15" s="32"/>
       <c r="H15" s="32"/>
@@ -1272,12 +1272,12 @@
         <v>209.99</v>
       </c>
       <c r="D16" s="19">
-        <f>C16*B16</f>
+        <f t="shared" si="1"/>
         <v>209.99</v>
       </c>
       <c r="E16" s="17">
-        <f>D16/($D$19+$D$24+$D$25+$B$29+$B$28)</f>
-        <v>4.1159423952902736E-3</v>
+        <f t="shared" si="0"/>
+        <v>4.1145502898108262E-3</v>
       </c>
       <c r="J16" s="32"/>
       <c r="K16" s="32"/>
@@ -1294,12 +1294,12 @@
         <v>48.87</v>
       </c>
       <c r="D17" s="19">
-        <f>C17*B17</f>
+        <f t="shared" si="1"/>
         <v>48.87</v>
       </c>
       <c r="E17" s="49">
-        <f>D17/($D$19+$D$24+$D$25+$B$29+$B$28)</f>
-        <v>9.5788420809484094E-4</v>
+        <f t="shared" si="0"/>
+        <v>9.5756022983501624E-4</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
@@ -1313,7 +1313,7 @@
         <v>-291.61</v>
       </c>
       <c r="D18" s="19">
-        <f>C18*B18</f>
+        <f t="shared" si="1"/>
         <v>-291.61</v>
       </c>
       <c r="E18" s="17">
@@ -1323,7 +1323,7 @@
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D19" s="20">
         <f>SUM(D2:D18)</f>
-        <v>48072.508310480007</v>
+        <v>49588.379832780003</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="E24" s="16">
         <f>D24/(D19+D24+D25+B28+B72)</f>
-        <v>1.9196825395759568E-2</v>
+        <v>1.9190320935658634E-2</v>
       </c>
       <c r="H24" s="45"/>
       <c r="J24" s="32"/>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="E25" s="16">
         <f>D25/(D19+D24+D25+B28+B29)</f>
-        <v>7.3714773883857962E-3</v>
+        <v>7.368984186810445E-3</v>
       </c>
       <c r="J25" s="32"/>
       <c r="K25" s="32"/>
@@ -1428,11 +1428,11 @@
         <v>38</v>
       </c>
       <c r="B28" s="7">
-        <v>1501</v>
+        <v>2.39</v>
       </c>
       <c r="C28" s="41">
         <f>B28/(D19+B29)</f>
-        <v>3.1164375624618063E-2</v>
+        <v>4.810804559846866E-5</v>
       </c>
       <c r="D28" s="25"/>
       <c r="E28" s="12"/>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="C29" s="41">
         <f>B29/D19</f>
-        <v>1.9025427050591685E-3</v>
+        <v>1.8443837106277283E-3</v>
       </c>
       <c r="D29" s="25"/>
       <c r="E29" s="12"/>
@@ -1509,7 +1509,7 @@
         <v>21287.19</v>
       </c>
       <c r="I32" s="15">
-        <v>20350.72</v>
+        <v>20091.53</v>
       </c>
       <c r="J32" s="32"/>
       <c r="K32" s="32"/>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="H33" s="32"/>
       <c r="I33" s="15">
-        <v>30104.35</v>
+        <v>30177.51</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -1564,8 +1564,8 @@
         <v>1164.81</v>
       </c>
       <c r="I34" s="15">
-        <f>66388*B25+ 66388*B24</f>
-        <v>1209.8157430799999</v>
+        <f xml:space="preserve"> 66038.49*B25+  66038.49*B24</f>
+        <v>1203.4464790509001</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="I36" s="34">
         <f>SUM(I32:I34)</f>
-        <v>51664.885743079998</v>
+        <v>51472.486479050895</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -1632,7 +1632,7 @@
       <c r="H37" s="9"/>
       <c r="I37" s="15">
         <f>D19+D24+D25+B28+B29</f>
-        <v>51018.692642609407</v>
+        <v>51035.954164909395</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -1650,32 +1650,32 @@
         <v>11</v>
       </c>
       <c r="B39" s="29">
-        <f t="shared" ref="B39:G39" si="0">B36-B37</f>
+        <f t="shared" ref="B39:G39" si="2">B36-B37</f>
         <v>2020.8500000000022</v>
       </c>
       <c r="C39" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>3260.630000000001</v>
       </c>
       <c r="D39" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2350.5800000000017</v>
       </c>
       <c r="E39" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>4382.239999999998</v>
       </c>
       <c r="F39" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>226.93000000000029</v>
       </c>
       <c r="G39" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1332.9199999999983</v>
       </c>
       <c r="I39" s="15">
         <f>I36-I37</f>
-        <v>646.19310047059116</v>
+        <v>436.53231414149923</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="I40" s="15">
         <f>I39*7.8</f>
-        <v>5040.3061836706111</v>
+        <v>3404.9520503036938</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="I42" s="16">
         <f>(I39/I37)</f>
-        <v>1.2665810647035446E-2</v>
+        <v>8.5534271139706478E-3</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
@@ -1806,7 +1806,7 @@
       <c r="H46" s="48"/>
       <c r="I46" s="37">
         <f>(I36-$B$36)/$B$36</f>
-        <v>1.2857150454082529</v>
+        <v>1.2772030766660072</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
